--- a/analyse-risque/EBIOS_RM_UniCampus.xlsx
+++ b/analyse-risque/EBIOS_RM_UniCampus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\virgi\Documents\Cours\2A\Cyber\Analyse de risques et projet de remédiation\Projet\analyse-risque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82C11CF-293C-4AC6-A046-F5D7A925D909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9C9BB6-D41C-49E8-AEA0-3B8CF836CAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,15 @@
     <sheet name="A1.2 Biens supports" sheetId="4" r:id="rId4"/>
     <sheet name="A1.3 Échelle de gravité" sheetId="5" r:id="rId5"/>
     <sheet name="A1.4 Événements redoutés" sheetId="6" r:id="rId6"/>
-    <sheet name="A2 Sources de risque" sheetId="7" r:id="rId7"/>
-    <sheet name="A3 Scénarios stratégiques" sheetId="8" r:id="rId8"/>
-    <sheet name="A4 Scénarios opérationnels" sheetId="9" r:id="rId9"/>
-    <sheet name="A5 Traitement du risque" sheetId="10" r:id="rId10"/>
+    <sheet name="A2.0 Échelle de pertinence" sheetId="7" r:id="rId7"/>
+    <sheet name="A2.1 Sources de risque" sheetId="8" r:id="rId8"/>
+    <sheet name="A2.2 Couples SR-OV" sheetId="9" r:id="rId9"/>
+    <sheet name="A2.3 Liens couples - ER" sheetId="10" r:id="rId10"/>
+    <sheet name="A3 Scénarios stratégiques" sheetId="11" r:id="rId11"/>
+    <sheet name="A4 Scénarios opérationnels" sheetId="12" r:id="rId12"/>
+    <sheet name="A5 Traitement du risque" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="398">
   <si>
     <t>Analyse de risque EBIOS RM : Classeur de travail</t>
   </si>
@@ -185,19 +188,37 @@
     <t>ER rattachés aux VM, cotation sur l'échelle</t>
   </si>
   <si>
-    <t>A2 Sources de risque</t>
-  </si>
-  <si>
-    <t>Couples SR/OV, pertinence</t>
+    <t>A2.0 Échelle de pertinence</t>
+  </si>
+  <si>
+    <t>Matrice 4×4 Motivation × Ressources → Pertinence + définitions des niveaux</t>
+  </si>
+  <si>
+    <t>A2.1 Sources de risque</t>
+  </si>
+  <si>
+    <t>Typologie des 5 sources de risque retenues avec profils</t>
+  </si>
+  <si>
+    <t>A2.2 Couples SR-OV</t>
+  </si>
+  <si>
+    <t>Couples évalués (motivation, ressources, pertinence calculée, décision)</t>
+  </si>
+  <si>
+    <t>A2.3 Liens couples - ER</t>
+  </si>
+  <si>
+    <t>Synthèse rapprochant les ER de A1.4 et les couples SR/OV</t>
+  </si>
+  <si>
+    <t>A3 Scénarios stratégiques</t>
+  </si>
+  <si>
+    <t>Parties prenantes, cartographie écosystème, scénarios haut niveau</t>
   </si>
   <si>
     <t>À produire</t>
-  </si>
-  <si>
-    <t>A3 Scénarios stratégiques</t>
-  </si>
-  <si>
-    <t>Parties prenantes, cartographie écosystème, scénarios haut niveau</t>
   </si>
   <si>
     <t>A4 Scénarios opérationnels</t>
@@ -705,6 +726,9 @@
     <t>A1.4 - Événements redoutés et niveau de gravité</t>
   </si>
   <si>
+    <t>Liste des événements redoutés (ER) identifiés au regard des valeurs métier listées en A1.1 et cotés sur l'échelle de gravité de A1.3. Chaque ER est formulé en termes métier (sans description technique) ; les scénarios techniques associés sont produits à l'atelier 4. Les catégories d'impact sont issues des six axes de répercussion EBIOS RM (missions, personnes, gouvernance, finances, juridique, image), enrichis ici de la catégorie « patrimoine intellectuel » pour la mission Recherche.</t>
+  </si>
+  <si>
     <t>Liste des événements redoutés</t>
   </si>
   <si>
@@ -841,10 +865,397 @@
     <t>Note : la gravité de ER04 est calibrée à G3 hors période d'examens et G4 pendant une session d'examens (basculement d'axe « Missions / activité » par franchissement du seuil G4 « arrêt d'un service vital »).</t>
   </si>
   <si>
-    <t>A2 — Sources de risque et objectifs visés</t>
-  </si>
-  <si>
-    <t>Cette feuille recevra les couples SR/OV avec leur motivation, ressources, pertinence et liaison aux ER.</t>
+    <t>A2.0 - Échelle de pertinence des couples SR/OV</t>
+  </si>
+  <si>
+    <t>Matrice de référence issue de la slide 31 du cours, permettant de déduire la pertinence d'un couple Source de risque / Objectif visé à partir de deux paramètres : la motivation de la source à atteindre son objectif et les ressources dont elle dispose. La pertinence prend l'une des quatre valeurs Peu pertinent / Moyennement pertinent / Plutôt pertinent / Très pertinent. Cette matrice est utilisée par formule dans la feuille A2.2 Couples SR/OV pour garantir la cohérence des évaluations.</t>
+  </si>
+  <si>
+    <t>Matrice Motivation × Ressources → Pertinence</t>
+  </si>
+  <si>
+    <t>RESSOURCES (ressources financières, compétences cyber, outillage, temps)</t>
+  </si>
+  <si>
+    <t>MOTIVATION</t>
+  </si>
+  <si>
+    <t>Ressources limitées</t>
+  </si>
+  <si>
+    <t>Ressources significatives</t>
+  </si>
+  <si>
+    <t>Ressources importantes</t>
+  </si>
+  <si>
+    <t>Ressources illimitées</t>
+  </si>
+  <si>
+    <t>Fortement motivé</t>
+  </si>
+  <si>
+    <t>Moyennement pertinent</t>
+  </si>
+  <si>
+    <t>Plutôt pertinent</t>
+  </si>
+  <si>
+    <t>Très pertinent</t>
+  </si>
+  <si>
+    <t>Assez motivé</t>
+  </si>
+  <si>
+    <t>Peu motivé</t>
+  </si>
+  <si>
+    <t>Peu pertinent</t>
+  </si>
+  <si>
+    <t>Très peu motivé</t>
+  </si>
+  <si>
+    <t>Définition des niveaux de motivation</t>
+  </si>
+  <si>
+    <t>Définition</t>
+  </si>
+  <si>
+    <t>Enjeu personnel direct, gain financier élevé, idéologie forte, intérêt stratégique majeur. La source poursuivra son objectif coûte que coûte.</t>
+  </si>
+  <si>
+    <t>Enjeu réel mais non vital. La source poursuivra son objectif si l'opportunité s'offre, mais pas à tout prix.</t>
+  </si>
+  <si>
+    <t>Intérêt opportuniste, défi ponctuel, curiosité. La source attaque si l'attaque est facile, sinon abandonne.</t>
+  </si>
+  <si>
+    <t>Pas d'intérêt direct envers l'objet d'étude. L'organisation pourrait être affectée comme dommage collatéral d'une attaque non ciblée.</t>
+  </si>
+  <si>
+    <t>Définition des niveaux de ressources</t>
+  </si>
+  <si>
+    <t>Outillage standard (Kali, scripts publics), compétences faibles à moyennes, temps disponible limité, pas de ressources financières dédiées à l'attaque.</t>
+  </si>
+  <si>
+    <t>Outillage avancé, compétences intermédiaires à fortes, temps disponible important. Profil typique : groupe organisé sans soutien étatique, insider qualifié, hacktiviste structuré.</t>
+  </si>
+  <si>
+    <t>Infrastructure d'attaque dédiée (C2, kits sur-mesure), compétences fortes, ressources financières conséquentes. Profil typique : groupe cybercriminel organisé (RaaS).</t>
+  </si>
+  <si>
+    <t>Capacités étatiques type APT : 0-days, ressources humaines et financières quasi sans limite, opérations longue durée, supply-chain attacks possibles.</t>
+  </si>
+  <si>
+    <t>Définition des niveaux de pertinence et décision associée</t>
+  </si>
+  <si>
+    <t>Pertinence</t>
+  </si>
+  <si>
+    <t>Signification</t>
+  </si>
+  <si>
+    <t>Décision suggérée</t>
+  </si>
+  <si>
+    <t>Couple théoriquement possible mais peu susceptible de se concrétiser : motivation faible et/ou ressources insuffisantes.</t>
+  </si>
+  <si>
+    <t>Écarté</t>
+  </si>
+  <si>
+    <t>Couple plausible mais non prioritaire. Mérite d'être surveillé pour détecter une évolution.</t>
+  </si>
+  <si>
+    <t>Surveillance</t>
+  </si>
+  <si>
+    <t>Couple probable à intégrer dans l'analyse des scénarios stratégiques (atelier 3).</t>
+  </si>
+  <si>
+    <t>Retenu</t>
+  </si>
+  <si>
+    <t>Couple hautement probable à intégrer prioritairement dans les scénarios stratégiques.</t>
+  </si>
+  <si>
+    <t>A2.1 - Sources de risque</t>
+  </si>
+  <si>
+    <t>Typologie des sources de risque retenues pour UniCampus+</t>
+  </si>
+  <si>
+    <t>Code SR</t>
+  </si>
+  <si>
+    <t>Profil</t>
+  </si>
+  <si>
+    <t>Description et profil sociologique</t>
+  </si>
+  <si>
+    <t>Capacités typiques</t>
+  </si>
+  <si>
+    <t>SR-A</t>
+  </si>
+  <si>
+    <t>Étudiant malveillant</t>
+  </si>
+  <si>
+    <t>Étudiant inscrit à UniCampus+. Profil hétérogène sur 12 000 individus : une fraction non négligeable dispose de compétences cyber réelles (Master Info, double cursus, autoformation). Bénéficie d'un accès physique au campus et au WiFi étudiants. Motivation typiquement personnelle (notes, examens) ou de défi.</t>
+  </si>
+  <si>
+    <t>Motivation variable selon l'OV ; ressources globalement significatives (compétences disponibles, temps illimité, accès interne).</t>
+  </si>
+  <si>
+    <t>SR-B</t>
+  </si>
+  <si>
+    <t>Cybercriminel organisé</t>
+  </si>
+  <si>
+    <t>Externe</t>
+  </si>
+  <si>
+    <t>Groupe cybercriminel à objectif financier (ransomware-as-a-service, revente de données). Cible opportuniste : UniCampus+ représente une cible attractive (budget public, données nombreuses, sécurité historiquement faible dans l'ESR français).</t>
+  </si>
+  <si>
+    <t>Motivation forte (gain financier) ; ressources importantes (kits ransomware matures, infrastructure C2).</t>
+  </si>
+  <si>
+    <t>SR-C</t>
+  </si>
+  <si>
+    <t>Acteur étatique / concurrent (APT)</t>
+  </si>
+  <si>
+    <t>Service de renseignement étranger ou concurrent industriel ciblant le patrimoine scientifique d'UniCampus+. Pertinence dépendant du caractère stratégique des recherches conduites (dual-use, IA, biotech, cryptographie…).</t>
+  </si>
+  <si>
+    <t>Motivation modérée à forte selon les domaines de recherche ; ressources illimitées (APT, supply-chain, 0-days).</t>
+  </si>
+  <si>
+    <t>SR-D</t>
+  </si>
+  <si>
+    <t>Hacktiviste</t>
+  </si>
+  <si>
+    <t>Individu ou collectif motivé par une cause idéologique (transparence, justice sociale, animaux de laboratoire, partenariats industriels controversés). Capable d'attaques médiatisées (défacement, fuites volontaires).</t>
+  </si>
+  <si>
+    <t>Motivation variable selon les causes pertinentes vis-à-vis d'UniCampus+ ; ressources significatives (compétences réelles, outillage public et privé).</t>
+  </si>
+  <si>
+    <t>SR-E</t>
+  </si>
+  <si>
+    <t>Personnel mécontent ou ex-personnel</t>
+  </si>
+  <si>
+    <t>Interne ou ex-interne</t>
+  </si>
+  <si>
+    <t>Membre ou ancien membre du personnel administratif, enseignant ou DSI, agissant par vengeance, fraude personnelle ou en réaction à un licenciement, une sanction ou un conflit. Bénéficie d'un accès légitime ou résiduel (compte non révoqué) et d'une connaissance fine du SI.</t>
+  </si>
+  <si>
+    <t>Motivation modérée à forte selon le contexte (fraude RH, vengeance) ; ressources significatives (accès interne, connaissance du SI).</t>
+  </si>
+  <si>
+    <t>A2.2 - Couples Source de risque / Objectif visé</t>
+  </si>
+  <si>
+    <t>Tableau des couples SR/OV évalués pour UniCampus+. Pour chaque couple, la pertinence est calculée par formule INDEX/MATCH depuis la matrice définie en A2.0 — pour modifier l'évaluation, changer Motivation et/ou Ressources via les listes déroulantes et la pertinence se met à jour automatiquement. La décision (Retenu / Surveillance / Écarté) suit en principe la pertinence (Plutôt et Très pertinent → Retenu ; Moyennement → Surveillance ; Peu → Écarté) mais peut être ajustée à dire d'expert. La colonne ER ciblé(s) fait le lien avec A1.4 et prépare A2.3.</t>
+  </si>
+  <si>
+    <t>Liste des couples SR/OV évalués</t>
+  </si>
+  <si>
+    <t>Code couple</t>
+  </si>
+  <si>
+    <t>Source de risque</t>
+  </si>
+  <si>
+    <t>Objectif visé</t>
+  </si>
+  <si>
+    <t>Motivation</t>
+  </si>
+  <si>
+    <t>Ressources</t>
+  </si>
+  <si>
+    <t>Pertinence (calculée)</t>
+  </si>
+  <si>
+    <t>Décision</t>
+  </si>
+  <si>
+    <t>ER ciblé(s)</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>SR-A Étudiant malveillant</t>
+  </si>
+  <si>
+    <t>Compromettre les résultats académiques (modifier notes, voler sujets d'examen)</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>Sabotage opportuniste (défi, curiosité, perturbation d'une session d'examens)</t>
+  </si>
+  <si>
+    <t>ER04, ER08</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>SR-B Cybercriminel organisé</t>
+  </si>
+  <si>
+    <t>Extorquer une rançon par chiffrement de l'infrastructure</t>
+  </si>
+  <si>
+    <t>ER06, ER04</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>Revendre les données personnelles des étudiants et personnels sur le marché noir</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>SR-C Acteur étatique / concurrent</t>
+  </si>
+  <si>
+    <t>Exfiltrer le patrimoine scientifique stratégique des laboratoires</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>SR-D Hacktiviste</t>
+  </si>
+  <si>
+    <t>Publier des données personnelles pour discréditer l'institution</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>Défacer la plateforme Moodle ou saboter l'image institutionnelle</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>SR-E Personnel mécontent ou ex-personnel</t>
+  </si>
+  <si>
+    <t>Détourner la paie ou frauder le système de gestion RH</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>Détruire ou altérer des données par vengeance</t>
+  </si>
+  <si>
+    <t>ER05, ER09</t>
+  </si>
+  <si>
+    <t>A2.3 - Liens entre les couples SR/OV et les événements redoutés</t>
+  </si>
+  <si>
+    <t>Synthèse rapprochant les événements redoutés de A1.4 et les couples SR/OV de A2.2 — équivalent du visuel de la slide 32 du cours. Pour chaque ER, on liste les couples qui le portent avec leur pertinence et leur décision. Cette synthèse alimente directement l'atelier 3 : seuls les couples Retenus sont déclinés en scénarios stratégiques. ER07 (usurpation d'identité) n'est associé à aucun couple en propre car il s'agit d'un événement pivot, étape intermédiaire dans la majorité des couples opérants (notamment C01, C03, C05, C08).</t>
+  </si>
+  <si>
+    <t>Couples SR/OV portant chaque événement redouté (triés par gravité descendante)</t>
+  </si>
+  <si>
+    <t>Couple SR/OV</t>
+  </si>
+  <si>
+    <t>Fuite massive des données personnelles des étudiants et personnels</t>
+  </si>
+  <si>
+    <t>SR-B Cybercriminel × Revente de données personnelles</t>
+  </si>
+  <si>
+    <t>SR-D Hacktiviste × Publication de données pour discrédit</t>
+  </si>
+  <si>
+    <t>Interruption massive et simultanée de l'ensemble des services numériques</t>
+  </si>
+  <si>
+    <t>SR-B Cybercriminel × Extorsion par rançongiciel</t>
+  </si>
+  <si>
+    <t>Fuite des données et résultats de recherche</t>
+  </si>
+  <si>
+    <t>SR-C Acteur étatique × Exfiltration du patrimoine scientifique</t>
+  </si>
+  <si>
+    <t>SR-A Étudiant × Compromission des résultats académiques</t>
+  </si>
+  <si>
+    <t>Interruption de l'accès aux services pédagogiques &gt; 24 h (notamment examens)</t>
+  </si>
+  <si>
+    <t>SR-B Cybercriminel × Extorsion par rançongiciel (effet de bord)</t>
+  </si>
+  <si>
+    <t>SR-A Étudiant × Sabotage opportuniste</t>
+  </si>
+  <si>
+    <t>SR-D Hacktiviste × Défacement / sabotage image</t>
+  </si>
+  <si>
+    <t>Altération frauduleuse de la paie et des données RH</t>
+  </si>
+  <si>
+    <t>SR-E Personnel mécontent × Détournement de la paie</t>
+  </si>
+  <si>
+    <t>SR-E Personnel mécontent × Vengeance par destruction (volet RH)</t>
+  </si>
+  <si>
+    <t>Usurpation d'identité d'un personnel ou enseignant (événement pivot)</t>
+  </si>
+  <si>
+    <t>Pivot : étape intermédiaire dans la majorité des couples opérants (notamment C01, C03, C05, C08)</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Perte ou destruction définitive des données de recherche</t>
+  </si>
+  <si>
+    <t>SR-E Personnel mécontent × Vengeance par destruction</t>
+  </si>
+  <si>
+    <t>Détournement de la messagerie pour campagnes externes malveillantes</t>
+  </si>
+  <si>
+    <t>SR-A Étudiant × Sabotage opportuniste (volet mail)</t>
+  </si>
+  <si>
+    <t>SR-D Hacktiviste × Défacement / sabotage image (volet mail)</t>
   </si>
   <si>
     <t>A3 — Scénarios stratégiques</t>
@@ -865,14 +1276,14 @@
     <t>Cette feuille recevra la matrice de risque, les mesures de traitement (techniques et organisationnelles), et la matrice de risque résiduel.</t>
   </si>
   <si>
-    <t>Liste des événements redoutés (ER) identifiés au regard des valeurs métier listées en A1.1 et cotés sur l'échelle de gravité de A1.3. Chaque ER est formulé en termes métier (sans description technique)</t>
+    <t>Liste des sources de risque (SR) candidates identifiées au regard du contexte d'UniCampus+. Chaque source est caractérisée par son profil (interne / externe), sa description sociologique et ses capacités typiques en termes de motivation et de ressources. Les couples SR/OV concrets sont construits en A2.2 à partir de cette typologie.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,8 +1371,15 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1022,6 +1440,12 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1063,8 +1487,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1130,6 +1566,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1185,12 +1624,77 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1234,7 +1738,7 @@
       <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFD699"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
@@ -1450,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1460,298 +1964,339 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="6" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="9" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="22" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="19" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="22" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="22" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="22" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="15" t="s">
+      <c r="B26" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="D26" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="21" t="s">
+      <c r="C29" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="101.35" x14ac:dyDescent="0.5">
+      <c r="A30" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="20" t="s">
+      <c r="C30" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="88.7" x14ac:dyDescent="0.5">
+      <c r="A31" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5"/>
+      <c r="C31" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A17:D17"/>
@@ -1768,6 +2313,350 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="55" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
@@ -1776,20 +2665,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="10"/>
+      <c r="A1" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="14"/>
     </row>
     <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
     </row>
     <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="9"/>
+      <c r="A4" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="B4" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:B4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+    </row>
+    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="B4" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:B4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+    </row>
+    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1812,93 +2771,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="A1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="A6" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>61</v>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="13">
+      <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>63</v>
+      <c r="B8" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="132" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="13">
+      <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>65</v>
+      <c r="B9" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="132" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="13">
+      <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>67</v>
+      <c r="B10" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="153.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="13">
+      <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>69</v>
+      <c r="B11" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="132" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="13">
+      <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>71</v>
+      <c r="B12" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1925,222 +2884,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="A1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="4" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="A4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>61</v>
+      <c r="A7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>83</v>
+      <c r="A8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>85</v>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>90</v>
+      <c r="E11" s="22" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>92</v>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>98</v>
+      <c r="E14" s="22" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>100</v>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>104</v>
+      <c r="A16" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>106</v>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>108</v>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>110</v>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2173,321 +3132,321 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="A1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="A4" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>118</v>
+      <c r="A7" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>124</v>
+      <c r="A8" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>124</v>
+      <c r="A9" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="F10" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="11" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>124</v>
+      <c r="A11" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>124</v>
+      <c r="A12" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>124</v>
+      <c r="E18" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>124</v>
+      <c r="A19" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>124</v>
+      <c r="A20" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2514,172 +3473,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="A1" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="A4" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="A6" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="A7" s="15" t="s">
         <v>184</v>
       </c>
+      <c r="B7" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="G8" s="27" t="s">
+      <c r="A8" s="30" t="s">
         <v>191</v>
       </c>
+      <c r="B8" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="30" t="s">
+      <c r="A9" s="33" t="s">
         <v>198</v>
       </c>
+      <c r="B9" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="33" t="s">
+      <c r="A10" s="36" t="s">
         <v>205</v>
       </c>
+      <c r="B10" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="G11" s="36" t="s">
+      <c r="A11" s="39" t="s">
         <v>212</v>
       </c>
+      <c r="B11" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2707,273 +3666,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="A1" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
+      <c r="A4" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
+      <c r="A6" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
+      <c r="A7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
+      <c r="A8" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
+      <c r="A9" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
     </row>
     <row r="11" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="A11" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+    </row>
+    <row r="12" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="5"/>
+      <c r="B12" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+    </row>
+    <row r="13" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+    </row>
+    <row r="14" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+    </row>
+    <row r="15" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+    </row>
+    <row r="16" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="6"/>
+      <c r="B16" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-    </row>
-    <row r="12" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-    </row>
-    <row r="13" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-    </row>
-    <row r="14" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-    </row>
-    <row r="15" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-    </row>
-    <row r="16" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
+      <c r="E16" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
     </row>
     <row r="18" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2992,33 +3951,372 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="10"/>
-    </row>
-    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="9"/>
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="4" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="E31" s="53"/>
+    </row>
+    <row r="32" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="E32" s="53"/>
+    </row>
+    <row r="33" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="53" t="s">
+        <v>297</v>
+      </c>
+      <c r="E33" s="53"/>
+    </row>
+    <row r="34" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="53" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:B4"/>
+  <mergeCells count="27">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3027,33 +4325,157 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="B1" s="10"/>
-    </row>
-    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B4" s="9"/>
+    <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>326</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:B4"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3062,35 +4484,383 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B1" s="10"/>
-    </row>
-    <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="4" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="9"/>
+    <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="4" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D8,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E8,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Plutôt pertinent</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D9,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E9,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Moyennement pertinent</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D10,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E10,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Très pertinent</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D11,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E11,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Plutôt pertinent</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F12" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D12,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E12,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Très pertinent</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D13,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E13,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Moyennement pertinent</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D14,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E14,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Moyennement pertinent</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D15,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E15,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Plutôt pertinent</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" s="17" t="str">
+        <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D16,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E16,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
+        <v>Plutôt pertinent</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>363</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:B4"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A6:H6"/>
   </mergeCells>
+  <conditionalFormatting sqref="F8:F16">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Peu pertinent"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Moyennement pertinent"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"Plutôt pertinent"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>"Très pertinent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" errorTitle="Valeur invalide" error="Choisir parmi : Retenu, Surveillance, Écarté." sqref="G8:G16" xr:uid="{00000000-0002-0000-0800-000002000000}">
+      <formula1>"Retenu,Surveillance,Écarté"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" errorTitle="Valeur invalide" error="Veuillez choisir une motivation dans la liste." xr:uid="{00000000-0002-0000-0800-000000000000}">
+          <x14:formula1>
+            <xm:f>'A2.0 Échelle de pertinence'!$A$10:$A$13</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>D8:D16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" errorTitle="Valeur invalide" error="Veuillez choisir un niveau de ressources dans la liste." xr:uid="{00000000-0002-0000-0800-000001000000}">
+          <x14:formula1>
+            <xm:f>'A2.0 Échelle de pertinence'!$B$9:$E$9</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>E8:E16</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/analyse-risque/EBIOS_RM_UniCampus.xlsx
+++ b/analyse-risque/EBIOS_RM_UniCampus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\virgi\Documents\Cours\2A\Cyber\Analyse de risques et projet de remédiation\Projet\analyse-risque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAF3259-F12D-4540-BCA0-C465393509A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C82145E-454E-43BF-9627-E0A5190DFE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -828,9 +828,6 @@
     <t>A2.0 - Échelle de pertinence des couples SR/OV</t>
   </si>
   <si>
-    <t>Matrice de référence issue de la slide 31 du cours, permettant de déduire la pertinence d'un couple Source de risque / Objectif visé à partir de deux paramètres : la motivation de la source à atteindre son objectif et les ressources dont elle dispose. La pertinence prend l'une des quatre valeurs Peu pertinent / Moyennement pertinent / Plutôt pertinent / Très pertinent. Cette matrice est utilisée par formule dans la feuille A2.2 Couples SR/OV pour garantir la cohérence des évaluations.</t>
-  </si>
-  <si>
     <t>Matrice Motivation × Ressources → Pertinence</t>
   </si>
   <si>
@@ -945,9 +942,6 @@
     <t>A2.1 - Sources de risque</t>
   </si>
   <si>
-    <t>Liste des sources de risque (SR) candidates identifiées au regard du contexte d'UniCampus+. Chaque source est caractérisée par son profil (interne / externe), sa description sociologique et ses capacités typiques en termes de motivation et de ressources. Les couples SR/OV concrets sont construits en A2.2 à partir de cette typologie. Les erreurs humaines et négligences non malveillantes ne sont pas traitées comme sources de risque ici (cf. doctrine EBIOS RM) — elles seront prises en compte au titre des vulnérabilités à l'atelier 4.</t>
-  </si>
-  <si>
     <t>Typologie des sources de risque retenues pour UniCampus+</t>
   </si>
   <si>
@@ -1032,9 +1026,6 @@
     <t>A2.2 - Couples Source de risque / Objectif visé</t>
   </si>
   <si>
-    <t>Tableau des couples SR/OV évalués pour UniCampus+. Pour chaque couple, la pertinence est calculée par formule INDEX/MATCH depuis la matrice définie en A2.0 — pour modifier l'évaluation, changer Motivation et/ou Ressources via les listes déroulantes et la pertinence se met à jour automatiquement. La décision (Retenu / Surveillance / Écarté) suit en principe la pertinence (Plutôt et Très pertinent → Retenu ; Moyennement → Surveillance ; Peu → Écarté) mais peut être ajustée à dire d'expert. La colonne ER ciblé(s) fait le lien avec A1.4 et prépare A2.3.</t>
-  </si>
-  <si>
     <t>Liste des couples SR/OV évalués</t>
   </si>
   <si>
@@ -1141,9 +1132,6 @@
   </si>
   <si>
     <t>A2.3 - Liens entre les couples SR/OV et les événements redoutés</t>
-  </si>
-  <si>
-    <t>Synthèse rapprochant les événements redoutés de A1.4 et les couples SR/OV de A2.2 — équivalent du visuel de la slide 32 du cours. Pour chaque ER, on liste les couples qui le portent avec leur pertinence et leur décision. Cette synthèse alimente directement l'atelier 3 : seuls les couples Retenus sont déclinés en scénarios stratégiques. ER07 (usurpation d'identité) n'est associé à aucun couple en propre car il s'agit d'un événement pivot, étape intermédiaire dans la majorité des couples opérants (notamment C01, C03, C05, C08).</t>
   </si>
   <si>
     <t>Couples SR/OV portant chaque événement redouté (triés par gravité descendante)</t>
@@ -3127,6 +3115,20 @@
   </si>
   <si>
     <t>Interruption de l'accès aux services pédagogiques pendant plus de 24 h</t>
+  </si>
+  <si>
+    <t>Matrice utiliséé pour determiner la pertinence d'un couple SR/OV à partir de la motivation et des ressources disponibles pour qu'un acteur accomplisse un certain objectif.</t>
+  </si>
+  <si>
+    <t>Liste des sources de risque identifiés au regard de l'entité Unicampus+. Cette liste (qui n'est pas en elle-même un livrable de l'atlier 2) sert à l'établissement des couples SR/OV.
+Nous notons qu'ils ne nous a pas parru pertinant de considerer les erreurs humaines comme une source de risque, ces dernières n'ayant aucune motivation ni capacité propre.</t>
+  </si>
+  <si>
+    <t>Première sortie de l'atelier  2 : Tableau des couples SR/OV évalués pour UniCampus+.</t>
+  </si>
+  <si>
+    <t>Seconde sortie de l'atlier 2 : Lien entre les différents couples SR//OV et les ER. Ce tableau est l'équivalent du visuel de la slide 32 du cours. 
+Lecture : Pour chaque ER, on liste les couples qui le portent avec leur pertinence par gravité descendante.</t>
   </si>
 </sst>
 </file>
@@ -3581,19 +3583,44 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3602,26 +3629,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3631,10 +3645,19 @@
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3643,16 +3666,10 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3661,32 +3678,17 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4395,50 +4397,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="59" t="s">
-        <v>948</v>
-      </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="A4" s="67" t="s">
+        <v>944</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
     </row>
     <row r="6" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
     </row>
     <row r="9" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
@@ -4462,7 +4464,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>47</v>
@@ -4473,13 +4475,13 @@
         <v>48</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="77" customHeight="1" x14ac:dyDescent="0.5">
@@ -4490,10 +4492,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
@@ -4504,10 +4506,10 @@
         <v>53</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
@@ -4525,12 +4527,12 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
@@ -4551,7 +4553,7 @@
         <v>62</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>63</v>
@@ -4596,7 +4598,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>66</v>
@@ -4610,7 +4612,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>66</v>
@@ -4638,7 +4640,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>66</v>
@@ -4693,8 +4695,8 @@
       <c r="B29" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="87" t="s">
-        <v>960</v>
+      <c r="C29" s="54" t="s">
+        <v>956</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>66</v>
@@ -4721,7 +4723,7 @@
       <c r="B31" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="54" t="s">
         <v>84</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -4763,8 +4765,8 @@
       <c r="B34" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="87" t="s">
-        <v>961</v>
+      <c r="C34" s="54" t="s">
+        <v>957</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>66</v>
@@ -4833,8 +4835,8 @@
       <c r="B39" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="87" t="s">
-        <v>962</v>
+      <c r="C39" s="54" t="s">
+        <v>958</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>66</v>
@@ -4861,7 +4863,7 @@
       <c r="B41" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="54" t="s">
         <v>102</v>
       </c>
       <c r="D41" s="5" t="s">
@@ -4910,42 +4912,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>976</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
@@ -4958,47 +4960,47 @@
         <v>218</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="78" t="s">
-        <v>357</v>
-      </c>
-      <c r="C8" s="76" t="s">
+      <c r="B8" s="80" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="83" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="63"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
@@ -5006,19 +5008,19 @@
         <v>245</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
@@ -5026,19 +5028,19 @@
         <v>230</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
@@ -5052,95 +5054,95 @@
         <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>361</v>
+      </c>
+      <c r="C13" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="F12" s="36" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="78" t="s">
+      <c r="F15" s="37" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="80" t="s">
         <v>365</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C16" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="D16" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="62"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="F16" s="36" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="61"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F17" s="36" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="63"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="75" t="s">
-        <v>241</v>
-      </c>
-      <c r="B16" s="78" t="s">
-        <v>369</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
@@ -5148,53 +5150,53 @@
         <v>233</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="81" t="s">
         <v>226</v>
       </c>
-      <c r="B19" s="78" t="s">
-        <v>374</v>
-      </c>
-      <c r="C19" s="77" t="s">
+      <c r="B19" s="80" t="s">
+        <v>370</v>
+      </c>
+      <c r="C19" s="84" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="63"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5230,65 +5232,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>378</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>379</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="39"/>
-      <c r="B7" s="73" t="s">
-        <v>380</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="73" t="s">
-        <v>381</v>
-      </c>
-      <c r="E7" s="55"/>
+      <c r="B7" s="77" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="59"/>
+      <c r="D7" s="77" t="s">
+        <v>377</v>
+      </c>
+      <c r="E7" s="59"/>
     </row>
     <row r="8" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5296,16 +5298,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5313,16 +5315,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5330,16 +5332,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5347,153 +5349,153 @@
         <v>4</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="65" t="s">
         <v>398</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="66" t="s">
-        <v>402</v>
-      </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
     </row>
     <row r="15" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="22" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>415</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="65" t="s">
         <v>417</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
     </row>
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>427</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>432</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>434</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -5524,173 +5526,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>437</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>438</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>434</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>439</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>435</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>446</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>463</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5721,104 +5723,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>474</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="84" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>475</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>476</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C8" s="10">
         <v>3</v>
@@ -5855,10 +5857,10 @@
     </row>
     <row r="9" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C9" s="11">
         <v>2</v>
@@ -5895,10 +5897,10 @@
     </row>
     <row r="10" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
@@ -5935,10 +5937,10 @@
     </row>
     <row r="11" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
@@ -5975,10 +5977,10 @@
     </row>
     <row r="12" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C12" s="10">
         <v>3</v>
@@ -6015,10 +6017,10 @@
     </row>
     <row r="13" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C13" s="11">
         <v>4</v>
@@ -6055,10 +6057,10 @@
     </row>
     <row r="14" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C14" s="10">
         <v>2</v>
@@ -6094,49 +6096,49 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="66" t="s">
-        <v>487</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
+      <c r="A16" s="65" t="s">
+        <v>483</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
     </row>
     <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="54" t="s">
-        <v>488</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
+      <c r="A17" s="68" t="s">
+        <v>484</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
     </row>
     <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="56" t="s">
-        <v>489</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
+      <c r="A19" s="66" t="s">
+        <v>485</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.5"/>
     <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.5"/>
@@ -6231,75 +6233,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>490</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>491</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>492</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>488</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>218</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>16</v>
@@ -6310,36 +6312,36 @@
     </row>
     <row r="9" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>9</v>
@@ -6350,16 +6352,16 @@
     </row>
     <row r="11" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>16</v>
@@ -6370,16 +6372,16 @@
     </row>
     <row r="12" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>16</v>
@@ -6390,22 +6392,22 @@
     </row>
     <row r="13" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>351</v>
-      </c>
       <c r="D13" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -6433,75 +6435,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>510</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>511</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>507</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>508</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E8" s="42">
         <v>2.25</v>
@@ -6512,16 +6514,16 @@
     </row>
     <row r="9" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E9" s="42">
         <v>1.5</v>
@@ -6532,16 +6534,16 @@
     </row>
     <row r="10" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E10" s="42">
         <v>0.44</v>
@@ -6552,16 +6554,16 @@
     </row>
     <row r="11" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E11" s="42">
         <v>0.22</v>
@@ -6571,24 +6573,24 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="66" t="s">
-        <v>525</v>
-      </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
+      <c r="A13" s="65" t="s">
+        <v>521</v>
+      </c>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="54" t="s">
-        <v>526</v>
-      </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
+      <c r="A14" s="68" t="s">
+        <v>522</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6614,30 +6616,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>527</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>523</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
     </row>
     <row r="4" spans="1:3" ht="84" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="79" t="s">
-        <v>528</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="72"/>
+      <c r="A4" s="85" t="s">
+        <v>524</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="76"/>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>529</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>525</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
     </row>
     <row r="7" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
@@ -6652,46 +6654,46 @@
     </row>
     <row r="8" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="25" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="16" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6715,290 +6717,299 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>542</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>538</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="4" spans="1:9" ht="139.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="79" t="s">
-        <v>543</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="72"/>
+      <c r="A4" s="85" t="s">
+        <v>539</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="76"/>
     </row>
     <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="66" t="s">
-        <v>544</v>
-      </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
+      <c r="A7" s="65" t="s">
+        <v>540</v>
+      </c>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
     </row>
     <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C53" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="55"/>
-      <c r="H53" s="55"/>
-      <c r="I53" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C53" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="76"/>
     </row>
     <row r="54" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B54" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="C54" s="78" t="s">
-        <v>548</v>
-      </c>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="72"/>
+        <v>543</v>
+      </c>
+      <c r="C54" s="80" t="s">
+        <v>544</v>
+      </c>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="76"/>
     </row>
     <row r="56" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A56" s="66" t="s">
-        <v>549</v>
-      </c>
-      <c r="B56" s="57"/>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
+      <c r="A56" s="65" t="s">
+        <v>545</v>
+      </c>
+      <c r="B56" s="64"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="64"/>
     </row>
     <row r="102" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C102" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D102" s="55"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="55"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="55"/>
-      <c r="I102" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C102" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="59"/>
+      <c r="I102" s="76"/>
     </row>
     <row r="103" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B103" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="C103" s="78" t="s">
-        <v>551</v>
-      </c>
-      <c r="D103" s="55"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="55"/>
-      <c r="I103" s="72"/>
+        <v>546</v>
+      </c>
+      <c r="C103" s="80" t="s">
+        <v>547</v>
+      </c>
+      <c r="D103" s="59"/>
+      <c r="E103" s="59"/>
+      <c r="F103" s="59"/>
+      <c r="G103" s="59"/>
+      <c r="H103" s="59"/>
+      <c r="I103" s="76"/>
     </row>
     <row r="105" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A105" s="66" t="s">
-        <v>552</v>
-      </c>
-      <c r="B105" s="57"/>
-      <c r="C105" s="57"/>
-      <c r="D105" s="57"/>
-      <c r="E105" s="57"/>
-      <c r="F105" s="57"/>
-      <c r="G105" s="57"/>
-      <c r="H105" s="57"/>
-      <c r="I105" s="57"/>
+      <c r="A105" s="65" t="s">
+        <v>548</v>
+      </c>
+      <c r="B105" s="64"/>
+      <c r="C105" s="64"/>
+      <c r="D105" s="64"/>
+      <c r="E105" s="64"/>
+      <c r="F105" s="64"/>
+      <c r="G105" s="64"/>
+      <c r="H105" s="64"/>
+      <c r="I105" s="64"/>
     </row>
     <row r="151" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B151" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C151" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D151" s="55"/>
-      <c r="E151" s="55"/>
-      <c r="F151" s="55"/>
-      <c r="G151" s="55"/>
-      <c r="H151" s="55"/>
-      <c r="I151" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C151" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D151" s="59"/>
+      <c r="E151" s="59"/>
+      <c r="F151" s="59"/>
+      <c r="G151" s="59"/>
+      <c r="H151" s="59"/>
+      <c r="I151" s="76"/>
     </row>
     <row r="152" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B152" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="C152" s="78" t="s">
-        <v>554</v>
-      </c>
-      <c r="D152" s="55"/>
-      <c r="E152" s="55"/>
-      <c r="F152" s="55"/>
-      <c r="G152" s="55"/>
-      <c r="H152" s="55"/>
-      <c r="I152" s="72"/>
+        <v>549</v>
+      </c>
+      <c r="C152" s="80" t="s">
+        <v>550</v>
+      </c>
+      <c r="D152" s="59"/>
+      <c r="E152" s="59"/>
+      <c r="F152" s="59"/>
+      <c r="G152" s="59"/>
+      <c r="H152" s="59"/>
+      <c r="I152" s="76"/>
     </row>
     <row r="154" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A154" s="66" t="s">
-        <v>555</v>
-      </c>
-      <c r="B154" s="57"/>
-      <c r="C154" s="57"/>
-      <c r="D154" s="57"/>
-      <c r="E154" s="57"/>
-      <c r="F154" s="57"/>
-      <c r="G154" s="57"/>
-      <c r="H154" s="57"/>
-      <c r="I154" s="57"/>
+      <c r="A154" s="65" t="s">
+        <v>551</v>
+      </c>
+      <c r="B154" s="64"/>
+      <c r="C154" s="64"/>
+      <c r="D154" s="64"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="64"/>
+      <c r="G154" s="64"/>
+      <c r="H154" s="64"/>
+      <c r="I154" s="64"/>
     </row>
     <row r="200" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B200" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C200" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D200" s="55"/>
-      <c r="E200" s="55"/>
-      <c r="F200" s="55"/>
-      <c r="G200" s="55"/>
-      <c r="H200" s="55"/>
-      <c r="I200" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C200" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D200" s="59"/>
+      <c r="E200" s="59"/>
+      <c r="F200" s="59"/>
+      <c r="G200" s="59"/>
+      <c r="H200" s="59"/>
+      <c r="I200" s="76"/>
     </row>
     <row r="201" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B201" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="C201" s="78" t="s">
-        <v>557</v>
-      </c>
-      <c r="D201" s="55"/>
-      <c r="E201" s="55"/>
-      <c r="F201" s="55"/>
-      <c r="G201" s="55"/>
-      <c r="H201" s="55"/>
-      <c r="I201" s="72"/>
+        <v>552</v>
+      </c>
+      <c r="C201" s="80" t="s">
+        <v>553</v>
+      </c>
+      <c r="D201" s="59"/>
+      <c r="E201" s="59"/>
+      <c r="F201" s="59"/>
+      <c r="G201" s="59"/>
+      <c r="H201" s="59"/>
+      <c r="I201" s="76"/>
     </row>
     <row r="203" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A203" s="66" t="s">
-        <v>558</v>
-      </c>
-      <c r="B203" s="57"/>
-      <c r="C203" s="57"/>
-      <c r="D203" s="57"/>
-      <c r="E203" s="57"/>
-      <c r="F203" s="57"/>
-      <c r="G203" s="57"/>
-      <c r="H203" s="57"/>
-      <c r="I203" s="57"/>
+      <c r="A203" s="65" t="s">
+        <v>554</v>
+      </c>
+      <c r="B203" s="64"/>
+      <c r="C203" s="64"/>
+      <c r="D203" s="64"/>
+      <c r="E203" s="64"/>
+      <c r="F203" s="64"/>
+      <c r="G203" s="64"/>
+      <c r="H203" s="64"/>
+      <c r="I203" s="64"/>
     </row>
     <row r="249" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B249" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C249" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D249" s="55"/>
-      <c r="E249" s="55"/>
-      <c r="F249" s="55"/>
-      <c r="G249" s="55"/>
-      <c r="H249" s="55"/>
-      <c r="I249" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C249" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D249" s="59"/>
+      <c r="E249" s="59"/>
+      <c r="F249" s="59"/>
+      <c r="G249" s="59"/>
+      <c r="H249" s="59"/>
+      <c r="I249" s="76"/>
     </row>
     <row r="250" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B250" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="C250" s="78" t="s">
-        <v>560</v>
-      </c>
-      <c r="D250" s="55"/>
-      <c r="E250" s="55"/>
-      <c r="F250" s="55"/>
-      <c r="G250" s="55"/>
-      <c r="H250" s="55"/>
-      <c r="I250" s="72"/>
+        <v>555</v>
+      </c>
+      <c r="C250" s="80" t="s">
+        <v>556</v>
+      </c>
+      <c r="D250" s="59"/>
+      <c r="E250" s="59"/>
+      <c r="F250" s="59"/>
+      <c r="G250" s="59"/>
+      <c r="H250" s="59"/>
+      <c r="I250" s="76"/>
     </row>
     <row r="252" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A252" s="66" t="s">
-        <v>561</v>
-      </c>
-      <c r="B252" s="57"/>
-      <c r="C252" s="57"/>
-      <c r="D252" s="57"/>
-      <c r="E252" s="57"/>
-      <c r="F252" s="57"/>
-      <c r="G252" s="57"/>
-      <c r="H252" s="57"/>
-      <c r="I252" s="57"/>
+      <c r="A252" s="65" t="s">
+        <v>557</v>
+      </c>
+      <c r="B252" s="64"/>
+      <c r="C252" s="64"/>
+      <c r="D252" s="64"/>
+      <c r="E252" s="64"/>
+      <c r="F252" s="64"/>
+      <c r="G252" s="64"/>
+      <c r="H252" s="64"/>
+      <c r="I252" s="64"/>
     </row>
     <row r="298" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B298" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C298" s="71" t="s">
-        <v>546</v>
-      </c>
-      <c r="D298" s="55"/>
-      <c r="E298" s="55"/>
-      <c r="F298" s="55"/>
-      <c r="G298" s="55"/>
-      <c r="H298" s="55"/>
-      <c r="I298" s="72"/>
+        <v>541</v>
+      </c>
+      <c r="C298" s="75" t="s">
+        <v>542</v>
+      </c>
+      <c r="D298" s="59"/>
+      <c r="E298" s="59"/>
+      <c r="F298" s="59"/>
+      <c r="G298" s="59"/>
+      <c r="H298" s="59"/>
+      <c r="I298" s="76"/>
     </row>
     <row r="299" spans="2:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B299" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="C299" s="78" t="s">
-        <v>563</v>
-      </c>
-      <c r="D299" s="55"/>
-      <c r="E299" s="55"/>
-      <c r="F299" s="55"/>
-      <c r="G299" s="55"/>
-      <c r="H299" s="55"/>
-      <c r="I299" s="72"/>
+        <v>558</v>
+      </c>
+      <c r="C299" s="80" t="s">
+        <v>559</v>
+      </c>
+      <c r="D299" s="59"/>
+      <c r="E299" s="59"/>
+      <c r="F299" s="59"/>
+      <c r="G299" s="59"/>
+      <c r="H299" s="59"/>
+      <c r="I299" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A252:I252"/>
+    <mergeCell ref="C299:I299"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A154:I154"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="C102:I102"/>
+    <mergeCell ref="C298:I298"/>
+    <mergeCell ref="C249:I249"/>
+    <mergeCell ref="A203:I203"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="C151:I151"/>
     <mergeCell ref="A4:I4"/>
@@ -7009,16 +7020,7 @@
     <mergeCell ref="C152:I152"/>
     <mergeCell ref="C201:I201"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A252:I252"/>
-    <mergeCell ref="C299:I299"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A154:I154"/>
-    <mergeCell ref="A105:I105"/>
     <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C102:I102"/>
-    <mergeCell ref="C298:I298"/>
-    <mergeCell ref="C249:I249"/>
-    <mergeCell ref="A203:I203"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7039,181 +7041,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>564</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="79" t="s">
-        <v>565</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="72"/>
+      <c r="A4" s="85" t="s">
+        <v>561</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="76"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>566</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>562</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -7237,231 +7239,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>587</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>588</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>585</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>588</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>591</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="F8" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>593</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>594</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>595</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>597</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>598</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>599</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>600</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>594</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C11" s="25" t="s">
+        <v>599</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>588</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>598</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="66" t="s">
-        <v>608</v>
-      </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
+      <c r="A13" s="65" t="s">
+        <v>604</v>
+      </c>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="25" t="s">
+        <v>608</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>612</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="F16" s="5" t="s">
         <v>618</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>625</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -7487,30 +7489,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
     </row>
     <row r="4" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1"/>
@@ -7550,8 +7552,8 @@
       <c r="B10" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="87" t="s">
-        <v>963</v>
+      <c r="C10" s="54" t="s">
+        <v>959</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="153.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -7561,7 +7563,7 @@
       <c r="B11" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="87" t="s">
+      <c r="C11" s="54" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7572,8 +7574,8 @@
       <c r="B12" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="87" t="s">
-        <v>964</v>
+      <c r="C12" s="54" t="s">
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -7601,244 +7603,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>628</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>624</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="4" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>629</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>625</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>630</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>626</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="66" t="s">
-        <v>656</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
+      <c r="A16" s="65" t="s">
+        <v>652</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7867,181 +7869,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>657</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>653</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>658</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>654</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>659</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>655</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>646</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>663</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>650</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -8073,510 +8075,510 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>670</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>671</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>667</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>672</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>668</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="H7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="86" t="s">
         <v>678</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="84" t="s">
-        <v>682</v>
-      </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
     </row>
     <row r="9" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="I9" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>689</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>692</v>
       </c>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="F10" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>692</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="H11" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>701</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="J11" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>692</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="G12" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>710</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>711</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="F13" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>713</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>718</v>
-      </c>
       <c r="I13" s="3" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="F14" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="H14" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="I14" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="90" t="s">
         <v>722</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>724</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>725</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>692</v>
-      </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="81" t="s">
-        <v>726</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="43" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="43" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="D17" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="F17" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J17" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G17" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I17" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J17" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K17" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="43" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D18" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F18" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J18" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G18" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="H18" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I18" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K18" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="43" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F19" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>739</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J19" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G19" s="45" t="s">
-        <v>743</v>
-      </c>
-      <c r="H19" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I19" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J19" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K19" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="43" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="F20" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>694</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J20" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G20" s="45" t="s">
-        <v>698</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I20" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J20" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K20" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="43" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D21" s="45" t="s">
         <v>162</v>
@@ -8585,598 +8587,598 @@
         <v>36</v>
       </c>
       <c r="F21" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>746</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J21" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G21" s="45" t="s">
-        <v>750</v>
-      </c>
-      <c r="H21" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I21" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J21" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K21" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="43" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D22" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="F22" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>685</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>721</v>
+      </c>
+      <c r="I22" s="43" t="s">
+        <v>700</v>
+      </c>
+      <c r="J22" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G22" s="45" t="s">
-        <v>689</v>
-      </c>
-      <c r="H22" s="45" t="s">
-        <v>725</v>
-      </c>
-      <c r="I22" s="43" t="s">
-        <v>704</v>
-      </c>
-      <c r="J22" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K22" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="43" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F23" s="43" t="s">
+        <v>684</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="H23" s="45" t="s">
+        <v>686</v>
+      </c>
+      <c r="I23" s="43" t="s">
+        <v>687</v>
+      </c>
+      <c r="J23" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="G23" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="H23" s="45" t="s">
-        <v>690</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>691</v>
-      </c>
-      <c r="J23" s="45" t="s">
-        <v>692</v>
-      </c>
       <c r="K23" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>759</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>760</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>761</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="80" t="s">
-        <v>766</v>
-      </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="A26" s="89" t="s">
+        <v>762</v>
+      </c>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="43" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G27" s="45" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H27" s="45" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I27" s="43" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J27" s="45" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K27" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="I30" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>780</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>782</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>783</v>
-      </c>
       <c r="J30" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="83" t="s">
-        <v>787</v>
-      </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
+      <c r="A32" s="88" t="s">
+        <v>783</v>
+      </c>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="43" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G33" s="45" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I33" s="43" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J33" s="45" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="J34" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>794</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>795</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>692</v>
       </c>
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="J35" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>692</v>
       </c>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="39" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="65" t="s">
+        <v>801</v>
+      </c>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="64"/>
+    </row>
+    <row r="40" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="87" t="s">
         <v>802</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="64"/>
+    </row>
+    <row r="41" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="87" t="s">
         <v>803</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>769</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="64"/>
+    </row>
+    <row r="42" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A42" s="87" t="s">
         <v>804</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>765</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>692</v>
-      </c>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="39" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="66" t="s">
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="64"/>
+    </row>
+    <row r="43" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A43" s="87" t="s">
         <v>805</v>
       </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-    </row>
-    <row r="40" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-    </row>
-    <row r="41" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="82" t="s">
-        <v>807</v>
-      </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-    </row>
-    <row r="42" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="82" t="s">
-        <v>808</v>
-      </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-    </row>
-    <row r="43" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="82" t="s">
-        <v>809</v>
-      </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -9210,108 +9212,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>810</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>806</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>811</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>807</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="85" t="s">
-        <v>812</v>
-      </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
+      <c r="A8" s="92" t="s">
+        <v>808</v>
+      </c>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>814</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B9" s="80" t="s">
+        <v>810</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="76"/>
     </row>
     <row r="10" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B10" s="78" t="s">
-        <v>816</v>
-      </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B10" s="80" t="s">
+        <v>812</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="76"/>
     </row>
     <row r="11" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B11" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="B11" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="72"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="76"/>
     </row>
     <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>819</v>
-      </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B12" s="80" t="s">
+        <v>815</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="76"/>
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E13" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E13" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F13" s="72"/>
+      <c r="F13" s="76"/>
     </row>
     <row r="14" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="48"/>
@@ -9324,130 +9326,130 @@
       <c r="D14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="86" t="s">
-        <v>825</v>
-      </c>
-      <c r="F14" s="72"/>
+      <c r="E14" s="91" t="s">
+        <v>821</v>
+      </c>
+      <c r="F14" s="76"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="48"/>
       <c r="B15" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>533</v>
-      </c>
-      <c r="E15" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F15" s="72"/>
+        <v>529</v>
+      </c>
+      <c r="E15" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F15" s="76"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="48"/>
       <c r="B16" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>642</v>
-      </c>
-      <c r="E16" s="86" t="s">
-        <v>828</v>
-      </c>
-      <c r="F16" s="72"/>
+        <v>638</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>824</v>
+      </c>
+      <c r="F16" s="76"/>
     </row>
     <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B17" s="78" t="s">
-        <v>830</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B17" s="80" t="s">
+        <v>826</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="76"/>
     </row>
     <row r="19" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="85" t="s">
-        <v>831</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
+      <c r="A19" s="92" t="s">
+        <v>827</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
     </row>
     <row r="20" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>832</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B20" s="80" t="s">
+        <v>828</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="76"/>
     </row>
     <row r="21" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>833</v>
-      </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B21" s="80" t="s">
+        <v>829</v>
+      </c>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="76"/>
     </row>
     <row r="22" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B22" s="86" t="s">
-        <v>336</v>
-      </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="72"/>
+        <v>813</v>
+      </c>
+      <c r="B22" s="91" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="76"/>
     </row>
     <row r="23" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>834</v>
-      </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>830</v>
+      </c>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="76"/>
     </row>
     <row r="24" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E24" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F24" s="72"/>
+      <c r="F24" s="76"/>
     </row>
     <row r="25" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="48"/>
@@ -9460,130 +9462,130 @@
       <c r="D25" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F25" s="72"/>
+      <c r="E25" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F25" s="76"/>
     </row>
     <row r="26" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="48"/>
       <c r="B26" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>533</v>
-      </c>
-      <c r="E26" s="86" t="s">
-        <v>835</v>
-      </c>
-      <c r="F26" s="72"/>
+        <v>529</v>
+      </c>
+      <c r="E26" s="91" t="s">
+        <v>831</v>
+      </c>
+      <c r="F26" s="76"/>
     </row>
     <row r="27" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="48"/>
       <c r="B27" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>642</v>
-      </c>
-      <c r="E27" s="86" t="s">
-        <v>836</v>
-      </c>
-      <c r="F27" s="72"/>
+        <v>638</v>
+      </c>
+      <c r="E27" s="91" t="s">
+        <v>832</v>
+      </c>
+      <c r="F27" s="76"/>
     </row>
     <row r="28" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B28" s="78" t="s">
-        <v>837</v>
-      </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B28" s="80" t="s">
+        <v>833</v>
+      </c>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="76"/>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="85" t="s">
-        <v>838</v>
-      </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
+      <c r="A30" s="92" t="s">
+        <v>834</v>
+      </c>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
     </row>
     <row r="31" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B31" s="78" t="s">
-        <v>839</v>
-      </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B31" s="80" t="s">
+        <v>835</v>
+      </c>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B32" s="78" t="s">
-        <v>840</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B32" s="80" t="s">
+        <v>836</v>
+      </c>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="76"/>
     </row>
     <row r="33" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B33" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="B33" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="72"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="76"/>
     </row>
     <row r="34" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B34" s="78" t="s">
-        <v>841</v>
-      </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B34" s="80" t="s">
+        <v>837</v>
+      </c>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="76"/>
     </row>
     <row r="35" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E35" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E35" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F35" s="72"/>
+      <c r="F35" s="76"/>
     </row>
     <row r="36" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="48"/>
@@ -9596,130 +9598,130 @@
       <c r="D36" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="86" t="s">
-        <v>825</v>
-      </c>
-      <c r="F36" s="72"/>
+      <c r="E36" s="91" t="s">
+        <v>821</v>
+      </c>
+      <c r="F36" s="76"/>
     </row>
     <row r="37" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="48"/>
       <c r="B37" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>533</v>
-      </c>
-      <c r="E37" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F37" s="72"/>
+        <v>529</v>
+      </c>
+      <c r="E37" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F37" s="76"/>
     </row>
     <row r="38" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="48"/>
       <c r="B38" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>647</v>
-      </c>
-      <c r="E38" s="86" t="s">
-        <v>842</v>
-      </c>
-      <c r="F38" s="72"/>
+        <v>643</v>
+      </c>
+      <c r="E38" s="91" t="s">
+        <v>838</v>
+      </c>
+      <c r="F38" s="76"/>
     </row>
     <row r="39" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B39" s="78" t="s">
-        <v>843</v>
-      </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B39" s="80" t="s">
+        <v>839</v>
+      </c>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="76"/>
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="85" t="s">
-        <v>844</v>
-      </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
+      <c r="A41" s="92" t="s">
+        <v>840</v>
+      </c>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
     </row>
     <row r="42" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B42" s="78" t="s">
-        <v>845</v>
-      </c>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B42" s="80" t="s">
+        <v>841</v>
+      </c>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A43" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B43" s="78" t="s">
-        <v>846</v>
-      </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B43" s="80" t="s">
+        <v>842</v>
+      </c>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="76"/>
     </row>
     <row r="44" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A44" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B44" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="B44" s="91" t="s">
         <v>230</v>
       </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="72"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="76"/>
     </row>
     <row r="45" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B45" s="78" t="s">
-        <v>847</v>
-      </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B45" s="80" t="s">
+        <v>843</v>
+      </c>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="76"/>
     </row>
     <row r="46" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E46" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E46" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F46" s="72"/>
+      <c r="F46" s="76"/>
     </row>
     <row r="47" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="48"/>
@@ -9732,130 +9734,130 @@
       <c r="D47" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="86" t="s">
-        <v>825</v>
-      </c>
-      <c r="F47" s="72"/>
+      <c r="E47" s="91" t="s">
+        <v>821</v>
+      </c>
+      <c r="F47" s="76"/>
     </row>
     <row r="48" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="48"/>
       <c r="B48" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="E48" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F48" s="72"/>
+        <v>526</v>
+      </c>
+      <c r="E48" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F48" s="76"/>
     </row>
     <row r="49" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="48"/>
       <c r="B49" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>650</v>
-      </c>
-      <c r="E49" s="86" t="s">
-        <v>848</v>
-      </c>
-      <c r="F49" s="72"/>
+        <v>646</v>
+      </c>
+      <c r="E49" s="91" t="s">
+        <v>844</v>
+      </c>
+      <c r="F49" s="76"/>
     </row>
     <row r="50" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B50" s="78" t="s">
-        <v>849</v>
-      </c>
-      <c r="C50" s="55"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B50" s="80" t="s">
+        <v>845</v>
+      </c>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="76"/>
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="85" t="s">
-        <v>850</v>
-      </c>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
+      <c r="A52" s="92" t="s">
+        <v>846</v>
+      </c>
+      <c r="B52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
     </row>
     <row r="53" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B53" s="78" t="s">
-        <v>851</v>
-      </c>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B53" s="80" t="s">
+        <v>847</v>
+      </c>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="76"/>
     </row>
     <row r="54" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B54" s="78" t="s">
-        <v>852</v>
-      </c>
-      <c r="C54" s="55"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B54" s="80" t="s">
+        <v>848</v>
+      </c>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="76"/>
     </row>
     <row r="55" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B55" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="B55" s="91" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="72"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="76"/>
     </row>
     <row r="56" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B56" s="78" t="s">
-        <v>853</v>
-      </c>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B56" s="80" t="s">
+        <v>849</v>
+      </c>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="76"/>
     </row>
     <row r="57" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A57" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E57" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E57" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F57" s="72"/>
+      <c r="F57" s="76"/>
     </row>
     <row r="58" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A58" s="48"/>
@@ -9868,130 +9870,130 @@
       <c r="D58" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E58" s="86" t="s">
-        <v>825</v>
-      </c>
-      <c r="F58" s="72"/>
+      <c r="E58" s="91" t="s">
+        <v>821</v>
+      </c>
+      <c r="F58" s="76"/>
     </row>
     <row r="59" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="48"/>
       <c r="B59" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="E59" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F59" s="72"/>
+        <v>526</v>
+      </c>
+      <c r="E59" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F59" s="76"/>
     </row>
     <row r="60" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="48"/>
       <c r="B60" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>650</v>
-      </c>
-      <c r="E60" s="86" t="s">
-        <v>848</v>
-      </c>
-      <c r="F60" s="72"/>
+        <v>646</v>
+      </c>
+      <c r="E60" s="91" t="s">
+        <v>844</v>
+      </c>
+      <c r="F60" s="76"/>
     </row>
     <row r="61" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B61" s="78" t="s">
-        <v>854</v>
-      </c>
-      <c r="C61" s="55"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B61" s="80" t="s">
+        <v>850</v>
+      </c>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="76"/>
     </row>
     <row r="63" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="85" t="s">
-        <v>855</v>
-      </c>
-      <c r="B63" s="57"/>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
+      <c r="A63" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="B63" s="64"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
     </row>
     <row r="64" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="B64" s="78" t="s">
-        <v>856</v>
-      </c>
-      <c r="C64" s="55"/>
-      <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="72"/>
+        <v>809</v>
+      </c>
+      <c r="B64" s="80" t="s">
+        <v>852</v>
+      </c>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="76"/>
     </row>
     <row r="65" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="46" t="s">
-        <v>815</v>
-      </c>
-      <c r="B65" s="78" t="s">
-        <v>857</v>
-      </c>
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="72"/>
+        <v>811</v>
+      </c>
+      <c r="B65" s="80" t="s">
+        <v>853</v>
+      </c>
+      <c r="C65" s="59"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="76"/>
     </row>
     <row r="66" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="46" t="s">
-        <v>817</v>
-      </c>
-      <c r="B66" s="86" t="s">
-        <v>352</v>
-      </c>
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="72"/>
+        <v>813</v>
+      </c>
+      <c r="B66" s="91" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="76"/>
     </row>
     <row r="67" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="46" t="s">
-        <v>818</v>
-      </c>
-      <c r="B67" s="78" t="s">
-        <v>858</v>
-      </c>
-      <c r="C67" s="55"/>
-      <c r="D67" s="55"/>
-      <c r="E67" s="55"/>
-      <c r="F67" s="72"/>
+        <v>814</v>
+      </c>
+      <c r="B67" s="80" t="s">
+        <v>854</v>
+      </c>
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="76"/>
     </row>
     <row r="68" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E68" s="75" t="s">
         <v>820</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E68" s="71" t="s">
-        <v>824</v>
-      </c>
-      <c r="F68" s="72"/>
+      <c r="F68" s="76"/>
     </row>
     <row r="69" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="48"/>
@@ -10004,57 +10006,103 @@
       <c r="D69" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F69" s="72"/>
+      <c r="E69" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F69" s="76"/>
     </row>
     <row r="70" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="48"/>
       <c r="B70" s="29" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="E70" s="86" t="s">
-        <v>826</v>
-      </c>
-      <c r="F70" s="72"/>
+        <v>526</v>
+      </c>
+      <c r="E70" s="91" t="s">
+        <v>822</v>
+      </c>
+      <c r="F70" s="76"/>
     </row>
     <row r="71" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="48"/>
       <c r="B71" s="29" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>655</v>
-      </c>
-      <c r="E71" s="86" t="s">
-        <v>859</v>
-      </c>
-      <c r="F71" s="72"/>
+        <v>651</v>
+      </c>
+      <c r="E71" s="91" t="s">
+        <v>855</v>
+      </c>
+      <c r="F71" s="76"/>
     </row>
     <row r="72" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A72" s="46" t="s">
-        <v>829</v>
-      </c>
-      <c r="B72" s="78" t="s">
-        <v>860</v>
-      </c>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="72"/>
+        <v>825</v>
+      </c>
+      <c r="B72" s="80" t="s">
+        <v>856</v>
+      </c>
+      <c r="C72" s="59"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E48:F48"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="B65:F65"/>
@@ -10071,52 +10119,6 @@
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10135,441 +10137,441 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>861</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>857</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>862</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>858</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
     </row>
     <row r="6" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>863</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>859</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="49" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="49" t="s">
+        <v>862</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>866</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>870</v>
-      </c>
       <c r="C9" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="49" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="33" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="33" t="s">
+        <v>871</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>874</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>869</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>875</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>878</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>873</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="33" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="33" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="51" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="51" t="s">
+        <v>880</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>883</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>869</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>884</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>887</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>873</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="51" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="51" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="52" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="52" t="s">
+        <v>889</v>
+      </c>
+      <c r="B20" s="47" t="s">
         <v>893</v>
       </c>
-      <c r="B20" s="47" t="s">
-        <v>897</v>
-      </c>
       <c r="C20" s="47" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="52" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="66" t="s">
-        <v>902</v>
-      </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
+      <c r="A24" s="65" t="s">
+        <v>898</v>
+      </c>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
     </row>
     <row r="25" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="29" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="29" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="53" t="s">
+        <v>913</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>914</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>915</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="65" t="s">
         <v>917</v>
       </c>
-      <c r="B29" s="50" t="s">
-        <v>918</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>919</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="66" t="s">
-        <v>921</v>
-      </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="29" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="53" t="s">
+        <v>921</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>924</v>
+      </c>
+      <c r="C34" s="50" t="s">
         <v>925</v>
       </c>
-      <c r="B34" s="50" t="s">
-        <v>928</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>929</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="29" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="53" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C36" s="50" t="s">
         <v>162</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="29" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="53" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="29" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B39" s="47" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
   </sheetData>
@@ -10598,38 +10600,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="88" t="s">
-        <v>970</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
+      <c r="A4" s="58" t="s">
+        <v>966</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
@@ -10649,11 +10651,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="61" t="s">
-        <v>965</v>
+      <c r="B8" s="70" t="s">
+        <v>961</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>125</v>
@@ -10666,8 +10668,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="62"/>
-      <c r="B9" s="62"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="15" t="s">
         <v>128</v>
       </c>
@@ -10679,21 +10681,21 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="62"/>
-      <c r="B10" s="62"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="14" t="s">
         <v>130</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="87" t="s">
-        <v>967</v>
+      <c r="E10" s="54" t="s">
+        <v>963</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="62"/>
-      <c r="B11" s="62"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="15" t="s">
         <v>132</v>
       </c>
@@ -10705,23 +10707,23 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="15" t="s">
         <v>134</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="89" t="s">
-        <v>966</v>
+      <c r="E12" s="55" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="70" t="s">
         <v>136</v>
       </c>
       <c r="C13" s="14" t="s">
@@ -10735,8 +10737,8 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="62"/>
-      <c r="B14" s="62"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="15" t="s">
         <v>139</v>
       </c>
@@ -10748,8 +10750,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="63"/>
-      <c r="B15" s="63"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="14" t="s">
         <v>141</v>
       </c>
@@ -10761,10 +10763,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="70" t="s">
         <v>144</v>
       </c>
       <c r="C16" s="15" t="s">
@@ -10778,8 +10780,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="62"/>
-      <c r="B17" s="62"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="14" t="s">
         <v>147</v>
       </c>
@@ -10791,33 +10793,35 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="89" t="s">
-        <v>969</v>
+      <c r="E18" s="55" t="s">
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="14" t="s">
         <v>150</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="87" t="s">
-        <v>968</v>
+      <c r="E19" s="54" t="s">
+        <v>964</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A19"/>
@@ -10825,8 +10829,6 @@
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10846,42 +10848,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="88" t="s">
-        <v>972</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="58" t="s">
+        <v>968</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
@@ -10907,10 +10909,10 @@
       <c r="A8" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="54" t="s">
         <v>160</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -10927,10 +10929,10 @@
       <c r="A9" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="89" t="s">
+      <c r="C9" s="55" t="s">
         <v>166</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -10996,8 +10998,8 @@
       <c r="D12" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="87" t="s">
-        <v>971</v>
+      <c r="E12" s="54" t="s">
+        <v>967</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>163</v>
@@ -11187,46 +11189,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="88" t="s">
-        <v>973</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
+      <c r="A4" s="58" t="s">
+        <v>969</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
     </row>
     <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
@@ -11368,23 +11370,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
       <c r="H2" s="28"/>
@@ -11400,13 +11402,13 @@
       <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="88" t="s">
-        <v>974</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
+      <c r="A4" s="58" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
       <c r="H4" s="28"/>
@@ -11422,13 +11424,13 @@
       <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
@@ -11474,14 +11476,14 @@
       <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="62" t="s">
         <v>223</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="92" t="s">
-        <v>976</v>
+      <c r="C9" s="57" t="s">
+        <v>972</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>225</v>
@@ -11494,7 +11496,7 @@
       <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="63"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="31" t="s">
         <v>226</v>
       </c>
@@ -11512,7 +11514,7 @@
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="60" t="s">
         <v>229</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -11532,7 +11534,7 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="63"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="3" t="s">
         <v>233</v>
       </c>
@@ -11593,7 +11595,7 @@
       <c r="A15" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="56" t="s">
         <v>245</v>
       </c>
       <c r="C15" s="32" t="s">
@@ -11610,13 +11612,13 @@
       <c r="H15" s="28"/>
     </row>
     <row r="17" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="88" t="s">
-        <v>975</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
+      <c r="A17" s="58" t="s">
+        <v>971</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11643,344 +11645,344 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="68" t="s">
+        <v>973</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-    </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+    </row>
+    <row r="8" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="77" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-    </row>
-    <row r="8" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
     </row>
     <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>255</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>260</v>
-      </c>
       <c r="E10" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B11" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>259</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>263</v>
-      </c>
       <c r="C12" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>259</v>
-      </c>
       <c r="E12" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="65" t="s">
         <v>264</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="66" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
     </row>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="71" t="s">
-        <v>266</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="72"/>
+      <c r="B16" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="76"/>
     </row>
     <row r="17" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
+        <v>256</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
     </row>
     <row r="18" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+        <v>260</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
     </row>
     <row r="19" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+        <v>261</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
     </row>
     <row r="20" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B20" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+    </row>
+    <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="65" t="s">
         <v>270</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-    </row>
-    <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="66" t="s">
-        <v>271</v>
-      </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
     </row>
     <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="71" t="s">
-        <v>266</v>
-      </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="72"/>
+      <c r="B23" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="76"/>
     </row>
     <row r="24" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="69" t="s">
-        <v>272</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
+        <v>252</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
     </row>
     <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" s="70" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
+        <v>253</v>
+      </c>
+      <c r="B25" s="78" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B26" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
+        <v>254</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
     </row>
     <row r="27" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B27" s="70" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="78" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-    </row>
-    <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="66" t="s">
-        <v>276</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B30" s="75" t="s">
         <v>277</v>
       </c>
-      <c r="B30" s="71" t="s">
+      <c r="C30" s="76"/>
+      <c r="D30" s="75" t="s">
         <v>278</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="71" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="72"/>
+      <c r="E30" s="76"/>
     </row>
     <row r="31" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="B31" s="69" t="s">
+        <v>262</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" s="59"/>
+      <c r="D31" s="79" t="s">
         <v>280</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="E31" s="55"/>
+      <c r="E31" s="59"/>
     </row>
     <row r="32" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="B32" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="C32" s="59"/>
+      <c r="D32" s="79" t="s">
         <v>282</v>
       </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="E32" s="55"/>
+      <c r="E32" s="59"/>
     </row>
     <row r="33" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="B33" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>283</v>
+      </c>
+      <c r="C33" s="59"/>
+      <c r="D33" s="79" t="s">
         <v>284</v>
       </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" s="55"/>
+      <c r="E33" s="59"/>
     </row>
     <row r="34" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="B34" s="69" t="s">
-        <v>286</v>
-      </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="74" t="s">
         <v>285</v>
       </c>
-      <c r="E34" s="55"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="79" t="s">
+        <v>284</v>
+      </c>
+      <c r="E34" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B25:E25"/>
@@ -11991,15 +11993,15 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12019,139 +12021,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+    </row>
+    <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="68" t="s">
+        <v>974</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-    </row>
-    <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-    </row>
-    <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-    </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>289</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>163</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="D9" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="E9" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="E10" s="5" t="s">
         <v>304</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="E11" s="8" t="s">
         <v>308</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="D12" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="E12" s="5" t="s">
         <v>313</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -12179,99 +12181,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="58" t="s">
-        <v>316</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="A1" s="63" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="4" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="54" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
+      <c r="A4" s="68" t="s">
+        <v>975</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
+      <c r="A6" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F8" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D8,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E8,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Plutôt pertinent</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>220</v>
@@ -12279,80 +12281,80 @@
     </row>
     <row r="9" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>331</v>
-      </c>
       <c r="D9" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F9" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D9,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E9,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Moyennement pertinent</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F10" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D10,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E10,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Très pertinent</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F11" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D11,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E11,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Plutôt pertinent</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>237</v>
@@ -12360,26 +12362,26 @@
     </row>
     <row r="12" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F12" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D12,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E12,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Très pertinent</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>230</v>
@@ -12387,26 +12389,26 @@
     </row>
     <row r="13" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F13" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D13,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E13,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Moyennement pertinent</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>237</v>
@@ -12414,53 +12416,53 @@
     </row>
     <row r="14" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>346</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F14" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D14,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E14,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Moyennement pertinent</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F15" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D15,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E15,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Plutôt pertinent</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>241</v>
@@ -12468,29 +12470,29 @@
     </row>
     <row r="16" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>351</v>
-      </c>
       <c r="D16" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F16" s="3" t="str">
         <f>IFERROR(INDEX('A2.0 Échelle de pertinence'!$B$10:$E$13,MATCH(D16,'A2.0 Échelle de pertinence'!$A$10:$A$13,0),MATCH(E16,'A2.0 Échelle de pertinence'!$B$9:$E$9,0)),"")</f>
         <v>Plutôt pertinent</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/analyse-risque/EBIOS_RM_UniCampus.xlsx
+++ b/analyse-risque/EBIOS_RM_UniCampus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\virgi\Documents\Cours\2A\Cyber\Analyse de risques et projet de remédiation\Projet\analyse-risque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C82145E-454E-43BF-9627-E0A5190DFE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F11074-A03B-4E45-8F66-6F0568F1F3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" tabRatio="500" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="980">
   <si>
     <t>A1.3 - Échelle de gravité (G1 à G4)</t>
   </si>
@@ -1203,9 +1203,6 @@
     <t>A3.0 - Critères d'évaluation de la dangerosité des parties prenantes</t>
   </si>
   <si>
-    <t>Échelles d'évaluation issues du guide ANSSI EBIOS RM (p.45-47) et de la slide 36 du cours 4CS08. Chaque partie prenante est notée de 1 à 4 sur quatre critères regroupés en deux blocs : l'EXPOSITION (Dépendance × Pénétration) et la FIABILITÉ CYBER (Maturité cyber × Confiance). Le niveau de dangerosité est calculé par la formule : Dangerosité = (Dépendance × Pénétration) / (Maturité × Confiance).</t>
-  </si>
-  <si>
     <t>Échelles d'évaluation (4 niveaux par critère)</t>
   </si>
   <si>
@@ -1383,9 +1380,6 @@
     <t>A3.1 - Parties prenantes de l'écosystème d'UniCampus+</t>
   </si>
   <si>
-    <t>Liste des parties prenantes (PP) externes identifiées dans l'écosystème d'UniCampus+. Conformément au guide ANSSI (p.91) : « un élément est une partie prenante si le commanditaire du périmètre de l'étude n'en est pas responsable ». Les étudiants, enseignants-chercheurs et personnels sont donc internes et ne figurent pas ici (ils ont été traités comme sources de risque en A2). Les clients au sens commercial n'existent pas pour une université publique — seules les catégories Partenaires et Prestataires sont retenues.</t>
-  </si>
-  <si>
     <t>Typologie des parties prenantes de l'écosystème</t>
   </si>
   <si>
@@ -1530,19 +1524,10 @@
     <t>RENATER (opérateur réseau ESR)</t>
   </si>
   <si>
-    <t>Synthèse — Parties prenantes critiques (PPC)</t>
-  </si>
-  <si>
-    <t>Les parties prenantes dont la colonne PPC indique « Oui » sont les Parties Prenantes Critiques (PPC) au sens ANSSI : elles seront intégrées prioritairement aux scénarios stratégiques de A3.3 et feront l'objet de mesures de sécurité spécifiques en A3.4. Les PP en zone Contrôle ne sont pas PPC mais doivent être surveillées.</t>
-  </si>
-  <si>
     <t>Visualisation radar de la cartographie (équivalent slide 37 du cours et p.47 du guide ANSSI)</t>
   </si>
   <si>
     <t>A3.3 - Scénarios stratégiques</t>
-  </si>
-  <si>
-    <t>Pour chaque couple SR/OV Retenu en A2.2, on construit un scénario stratégique de haut niveau qui décrit 1 à 3 chemins d'attaque (attaque directe ou rebond via une PPC). Format inspiré du guide ANSSI p.52. La gravité est héritée de l'événement redouté associé en A1.4 (slide 32 du cours). Les chemins par rebond ciblent en priorité les parties prenantes en zone de danger ou de contrôle élevée identifiées en A3.2. Les scénarios stratégiques retenus ici servent d'entrée à l'atelier 4 (scénarios opérationnels).</t>
   </si>
   <si>
     <t>Scénarios stratégiques retenus (un par couple SR/OV)</t>
@@ -1637,23 +1622,7 @@
     <t>Déploiement de rançongiciel par supply-chain (SS2 chemin 2) ; exfiltration de données via télémaintenance (SS3 chemin 2)</t>
   </si>
   <si>
-    <t>Accroître la maturité cyber et la confiance des prestataires logiciels :
-• inclure dans les contrats des clauses cyber (RGPD, notification d'incident &lt; 72 h, audit de sécurité périodique, droit d'audit) ;
-• vérifier la signature des correctifs et mises à jour avant déploiement ;
-• imposer un accès distant via un canal authentifié et journalisé (suppression de tout accès permanent non maîtrisé) ;
-• exiger une attestation de conformité (ISO 27001 ou équivalent) pour les éditeurs de logiciels métier sensibles (RH notamment).
-Effet attendu : Maturité 2 → 3, Confiance 2 → 3 ; pénétration inchangée.</t>
-  </si>
-  <si>
     <t>Exfiltration du patrimoine scientifique par rebond (SS4 chemin 2) ; destruction collatérale par personnel mécontent (SS6 chemin 2)</t>
-  </si>
-  <si>
-    <t>Diminuer la pénétration des laboratoires partenaires et accroître leur maturité cyber :
-• limiter strictement le partage de données au juste besoin (principe du moindre privilège) — actuellement, les données partagées via NFS/Samba sont accessibles trop largement ;
-• cloisonner les espaces de partage par projet / convention ;
-• inclure dans les conventions de collaboration des clauses sur la sécurité des données (chiffrement, traçabilité, notification d'incident) ;
-• organiser des audits croisés ponctuels sur les partages de données les plus sensibles.
-Effet attendu : Pénétration 3 → 2.</t>
   </si>
   <si>
     <t>Exfiltration du patrimoine scientifique par rebond (SS4 chemin 3)</t>
@@ -3129,6 +3098,50 @@
   <si>
     <t>Seconde sortie de l'atlier 2 : Lien entre les différents couples SR//OV et les ER. Ce tableau est l'équivalent du visuel de la slide 32 du cours. 
 Lecture : Pour chaque ER, on liste les couples qui le portent avec leur pertinence par gravité descendante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Échelles d'évaluation des risques associés aux parties prenantes PP exterieurs (prestataires/ partenaires) en fonction des 4 critères vue dans le cours.
+Le premier tableau sert d'indication pour caractériser les différents niveaux de risques. 
+Les deux tableaux suivants définissent des seuils precis utilisés pour les rendus de l'atelier 3.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendu de l'atelier 3 : Liste des parties prenantes (PP) externes identifiées dans l'écosystème d'UniCampus+. </t>
+  </si>
+  <si>
+    <t>Synthèse - Parties prenantes critiques (PPC)</t>
+  </si>
+  <si>
+    <t>Les parties prenantes dont la colonne PPC indique « Oui » sont les Parties Prenantes Critiques (PPC) au sens ANSSI : elles seront intégrées prioritairement aux scénarios stratégiques de A3.3 et feront l'objet de mesures de sécurité spécifiques en A3.4. Les PP en zone Contrôle ne sont pas PPC mais doivent être surveillées.
+Au vue de cette analyse, aucune partie prenante n'est identifé comme critique. Cela peut se justifier par le fait que l'entité Unicampus, dans la modélisation que nous en avons faites est particulièrement autonome et dont les partenaires possède un niveau de confiance relativement élevé.</t>
+  </si>
+  <si>
+    <t>Second rendu pour l'atelier 3 : Pour chaque couple SR/OV Retenu en A2.2, on construit un scénario stratégique de haut niveau qui décrit 1 à 3 chemins d'attaque (attaque directe ou rebond via une PPC). Format inspiré du guide ANSSI p.52. La gravité est héritée de l'événement redouté associé en A1.4 (slide 32 du cours). Les chemins par rebond ciblent en priorité les parties prenantes en zone de danger ou de contrôle élevée identifiées en A3.2. Les scénarios stratégiques retenus ici servent d'entrée à l'atelier 4 (scénarios opérationnels).</t>
+  </si>
+  <si>
+    <t>Code SR/OV</t>
+  </si>
+  <si>
+    <t>CR08</t>
+  </si>
+  <si>
+    <t>CR09</t>
+  </si>
+  <si>
+    <t>Diminuer la pénétration des laboratoires partenaires et accroître leur maturité cyber :
+• limiter strictement le partage de données au juste besoin (principe du moindre privilège) actuellement, les données partagées via NFS/Samba sont accessibles trop largement ;
+• cloisonner les espaces de partage par projet / convention ;
+• inclure dans les conventions de collaboration des clauses sur la sécurité des données (chiffrement, traçabilité, notification d'incident) ;
+• organiser des audits croisés ponctuels sur les partages de données les plus sensibles.
+Effet attendu : Pénétration 3 → 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accroître la maturité cyber et la confiance des prestataires logiciels :
+• inclure dans les contrats des clauses cyber (RGPD, notification d'incident &lt; 72 h, audit de sécurité périodique, droit d'audit) ;
+• vérifier la signature des correctifs et mises à jour avant déploiement ;
+• imposer un accès distant via un canal authentifié et journalisé (suppression de tout accès permanent non maîtrisé) ;
+• exiger une attestation de conformité (ISO 27001 ou équivalent) pour les éditeurs de logiciels métier sensibles (RH notamment).
+Effet attendu : Maturité 2 → 3, Confiance 2  → 3 </t>
   </si>
 </sst>
 </file>
@@ -3430,7 +3443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3689,6 +3702,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4412,7 +4428,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="67" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -4464,7 +4480,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>47</v>
@@ -4475,13 +4491,13 @@
         <v>48</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="77" customHeight="1" x14ac:dyDescent="0.5">
@@ -4492,10 +4508,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
@@ -4506,10 +4522,10 @@
         <v>53</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.5">
@@ -4553,7 +4569,7 @@
         <v>62</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>63</v>
@@ -4598,7 +4614,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>66</v>
@@ -4612,7 +4628,7 @@
         <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>66</v>
@@ -4640,7 +4656,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>66</v>
@@ -4696,7 +4712,7 @@
         <v>50</v>
       </c>
       <c r="C29" s="54" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>66</v>
@@ -4766,7 +4782,7 @@
         <v>52</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>66</v>
@@ -4836,7 +4852,7 @@
         <v>54</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>66</v>
@@ -4931,7 +4947,7 @@
     </row>
     <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -5227,7 +5243,7 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="17.9375" customWidth="1"/>
     <col min="2" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5249,7 +5265,7 @@
     </row>
     <row r="4" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>374</v>
+        <v>970</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -5258,7 +5274,7 @@
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -5268,11 +5284,11 @@
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="39"/>
       <c r="B7" s="77" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="77" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E7" s="59"/>
     </row>
@@ -5281,16 +5297,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5298,16 +5314,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>384</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5315,16 +5331,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>388</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5332,16 +5348,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -5349,21 +5365,21 @@
         <v>4</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>396</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="65" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B14" s="64"/>
       <c r="C14" s="64"/>
@@ -5372,75 +5388,75 @@
     </row>
     <row r="15" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="E16" s="5" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="39.35" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="22" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="22" t="s">
+      <c r="B17" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="E17" s="5" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="41.35" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="16" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="C18" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="5" t="s">
         <v>415</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="65" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B20" s="64"/>
       <c r="C20" s="64"/>
@@ -5449,53 +5465,53 @@
     </row>
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="3" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="C22" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="D22" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="E22" s="10" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="7" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="7" t="s">
+      <c r="B23" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>431</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -5527,7 +5543,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -5543,7 +5559,7 @@
     </row>
     <row r="4" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>434</v>
+        <v>971</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -5552,7 +5568,7 @@
     </row>
     <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -5561,138 +5577,138 @@
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="D8" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="E8" s="5" t="s">
         <v>442</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="C9" s="35" t="s">
+      <c r="E9" s="8" t="s">
         <v>446</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="C10" s="34" t="s">
+      <c r="E10" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="C11" s="35" t="s">
+      <c r="E11" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="D12" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="E12" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="C13" s="35" t="s">
+      <c r="E13" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="C14" s="34" t="s">
+      <c r="E14" s="5" t="s">
         <v>467</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5724,7 +5740,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -5752,7 +5768,7 @@
     </row>
     <row r="4" spans="1:11" ht="84" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -5767,7 +5783,7 @@
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -5782,45 +5798,45 @@
     </row>
     <row r="7" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>440</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>442</v>
       </c>
       <c r="C8" s="10">
         <v>3</v>
@@ -5857,10 +5873,10 @@
     </row>
     <row r="9" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C9" s="11">
         <v>2</v>
@@ -5897,10 +5913,10 @@
     </row>
     <row r="10" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
@@ -5937,10 +5953,10 @@
     </row>
     <row r="11" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
@@ -5977,10 +5993,10 @@
     </row>
     <row r="12" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="C12" s="10">
         <v>3</v>
@@ -6017,10 +6033,10 @@
     </row>
     <row r="13" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C13" s="11">
         <v>4</v>
@@ -6057,10 +6073,10 @@
     </row>
     <row r="14" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C14" s="10">
         <v>2</v>
@@ -6097,7 +6113,7 @@
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="65" t="s">
-        <v>483</v>
+        <v>972</v>
       </c>
       <c r="B16" s="64"/>
       <c r="C16" s="64"/>
@@ -6110,9 +6126,9 @@
       <c r="J16" s="64"/>
       <c r="K16" s="64"/>
     </row>
-    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" ht="71.349999999999994" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="68" t="s">
-        <v>484</v>
+        <v>973</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="59"/>
@@ -6127,7 +6143,7 @@
     </row>
     <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="66" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B19" s="64"/>
       <c r="C19" s="64"/>
@@ -6221,200 +6237,225 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="64"/>
+        <v>482</v>
+      </c>
+      <c r="B1" s="63"/>
       <c r="C1" s="64"/>
       <c r="D1" s="64"/>
       <c r="E1" s="64"/>
       <c r="F1" s="64"/>
-    </row>
-    <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G1" s="64"/>
+    </row>
+    <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="64"/>
       <c r="B2" s="64"/>
       <c r="C2" s="64"/>
       <c r="D2" s="64"/>
       <c r="E2" s="64"/>
       <c r="F2" s="64"/>
-    </row>
-    <row r="4" spans="1:6" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G2" s="64"/>
+    </row>
+    <row r="4" spans="1:7" ht="87.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>487</v>
-      </c>
-      <c r="B4" s="59"/>
+        <v>974</v>
+      </c>
+      <c r="B4" s="93"/>
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="59"/>
       <c r="F4" s="59"/>
-    </row>
-    <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G4" s="59"/>
+    </row>
+    <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>488</v>
-      </c>
-      <c r="B6" s="64"/>
+        <v>483</v>
+      </c>
+      <c r="B6" s="65"/>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
-    </row>
-    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G6" s="64"/>
+    </row>
+    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B9" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="F9" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="3" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="F10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="G11" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="7" t="s">
+      <c r="F12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B13" s="7" t="s">
+        <v>977</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="E11" s="19" t="s">
+      <c r="F13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>349</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6436,7 +6477,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -6454,7 +6495,7 @@
     </row>
     <row r="4" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -6464,7 +6505,7 @@
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -6474,36 +6515,36 @@
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>459</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>514</v>
+        <v>979</v>
       </c>
       <c r="E8" s="42">
         <v>2.25</v>
@@ -6514,16 +6555,16 @@
     </row>
     <row r="9" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>442</v>
-      </c>
       <c r="C9" s="8" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>516</v>
+        <v>978</v>
       </c>
       <c r="E9" s="42">
         <v>1.5</v>
@@ -6534,16 +6575,16 @@
     </row>
     <row r="10" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E10" s="42">
         <v>0.44</v>
@@ -6554,16 +6595,16 @@
     </row>
     <row r="11" spans="1:6" ht="159.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E11" s="42">
         <v>0.22</v>
@@ -6574,7 +6615,7 @@
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="65" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B13" s="64"/>
       <c r="C13" s="64"/>
@@ -6584,7 +6625,7 @@
     </row>
     <row r="14" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="68" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
@@ -6617,7 +6658,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -6629,14 +6670,14 @@
     </row>
     <row r="4" spans="1:3" ht="84" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="85" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="76"/>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -6654,46 +6695,46 @@
     </row>
     <row r="8" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="16" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -6718,7 +6759,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -6742,7 +6783,7 @@
     </row>
     <row r="4" spans="1:9" ht="139.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="85" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -6755,7 +6796,7 @@
     </row>
     <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="65" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="64"/>
@@ -6768,10 +6809,10 @@
     </row>
     <row r="53" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B53" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C53" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D53" s="59"/>
       <c r="E53" s="59"/>
@@ -6782,10 +6823,10 @@
     </row>
     <row r="54" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B54" s="5" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="C54" s="80" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D54" s="59"/>
       <c r="E54" s="59"/>
@@ -6796,7 +6837,7 @@
     </row>
     <row r="56" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="65" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B56" s="64"/>
       <c r="C56" s="64"/>
@@ -6809,10 +6850,10 @@
     </row>
     <row r="102" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B102" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C102" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D102" s="59"/>
       <c r="E102" s="59"/>
@@ -6823,10 +6864,10 @@
     </row>
     <row r="103" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B103" s="5" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="C103" s="80" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="D103" s="59"/>
       <c r="E103" s="59"/>
@@ -6837,7 +6878,7 @@
     </row>
     <row r="105" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A105" s="65" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="B105" s="64"/>
       <c r="C105" s="64"/>
@@ -6850,10 +6891,10 @@
     </row>
     <row r="151" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B151" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C151" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D151" s="59"/>
       <c r="E151" s="59"/>
@@ -6864,10 +6905,10 @@
     </row>
     <row r="152" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B152" s="5" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C152" s="80" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="D152" s="59"/>
       <c r="E152" s="59"/>
@@ -6878,7 +6919,7 @@
     </row>
     <row r="154" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A154" s="65" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B154" s="64"/>
       <c r="C154" s="64"/>
@@ -6891,10 +6932,10 @@
     </row>
     <row r="200" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B200" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C200" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D200" s="59"/>
       <c r="E200" s="59"/>
@@ -6905,10 +6946,10 @@
     </row>
     <row r="201" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B201" s="5" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C201" s="80" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D201" s="59"/>
       <c r="E201" s="59"/>
@@ -6919,7 +6960,7 @@
     </row>
     <row r="203" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A203" s="65" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B203" s="64"/>
       <c r="C203" s="64"/>
@@ -6932,10 +6973,10 @@
     </row>
     <row r="249" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B249" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C249" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D249" s="59"/>
       <c r="E249" s="59"/>
@@ -6946,10 +6987,10 @@
     </row>
     <row r="250" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B250" s="5" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C250" s="80" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="D250" s="59"/>
       <c r="E250" s="59"/>
@@ -6960,7 +7001,7 @@
     </row>
     <row r="252" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A252" s="65" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B252" s="64"/>
       <c r="C252" s="64"/>
@@ -6973,10 +7014,10 @@
     </row>
     <row r="298" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B298" s="1" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C298" s="75" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D298" s="59"/>
       <c r="E298" s="59"/>
@@ -6987,10 +7028,10 @@
     </row>
     <row r="299" spans="2:9" ht="108" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B299" s="5" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C299" s="80" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="D299" s="59"/>
       <c r="E299" s="59"/>
@@ -7042,7 +7083,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -7060,7 +7101,7 @@
     </row>
     <row r="4" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="85" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -7070,7 +7111,7 @@
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -7080,142 +7121,142 @@
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>317</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>331</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>331</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>337</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>345</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>345</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -7240,7 +7281,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -7258,7 +7299,7 @@
     </row>
     <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -7268,7 +7309,7 @@
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -7278,107 +7319,107 @@
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E9" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C10" s="25" t="s">
+        <v>581</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>588</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>595</v>
-      </c>
       <c r="E10" s="22" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="65" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B13" s="64"/>
       <c r="C13" s="64"/>
@@ -7391,79 +7432,79 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>322</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="25" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="22" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="16" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -7553,7 +7594,7 @@
         <v>114</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="153.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -7575,7 +7616,7 @@
         <v>117</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -7604,7 +7645,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -7626,7 +7667,7 @@
     </row>
     <row r="4" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -7638,7 +7679,7 @@
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -7650,189 +7691,189 @@
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="65" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B16" s="64"/>
       <c r="C16" s="64"/>
@@ -7870,7 +7911,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -7888,7 +7929,7 @@
     </row>
     <row r="4" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -7898,7 +7939,7 @@
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -7908,142 +7949,142 @@
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -8076,7 +8117,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -8104,7 +8145,7 @@
     </row>
     <row r="4" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -8119,7 +8160,7 @@
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -8134,42 +8175,42 @@
     </row>
     <row r="7" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="86" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B8" s="64"/>
       <c r="C8" s="64"/>
@@ -8184,205 +8225,205 @@
     </row>
     <row r="9" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="I9" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="J9" s="10" t="s">
         <v>681</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>685</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>688</v>
       </c>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>699</v>
-      </c>
       <c r="H11" s="10" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="90" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B15" s="64"/>
       <c r="C15" s="64"/>
@@ -8397,188 +8438,188 @@
     </row>
     <row r="16" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="43" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H16" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>680</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="K16" s="43" t="s">
         <v>721</v>
-      </c>
-      <c r="I16" s="43" t="s">
-        <v>687</v>
-      </c>
-      <c r="J16" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="43" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="D17" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G17" s="45" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H17" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I17" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="43" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="D18" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H18" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I18" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J18" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="43" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="H19" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I19" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="43" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="H20" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="43" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D21" s="45" t="s">
         <v>162</v>
@@ -8587,163 +8628,163 @@
         <v>36</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G21" s="45" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H21" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I21" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="43" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="D22" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="H22" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="I22" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="K22" s="43" t="s">
         <v>721</v>
-      </c>
-      <c r="I22" s="43" t="s">
-        <v>700</v>
-      </c>
-      <c r="J22" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="K22" s="43" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="43" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G23" s="45" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I23" s="43" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J23" s="45" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K23" s="43" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="89" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B26" s="64"/>
       <c r="C26" s="64"/>
@@ -8758,174 +8799,174 @@
     </row>
     <row r="27" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="43" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G27" s="45" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H27" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="I27" s="43" t="s">
+        <v>680</v>
+      </c>
+      <c r="J27" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="K27" s="43" t="s">
         <v>721</v>
-      </c>
-      <c r="I27" s="43" t="s">
-        <v>687</v>
-      </c>
-      <c r="J27" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="K27" s="43" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="C29" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>711</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>772</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="88" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="B32" s="64"/>
       <c r="C32" s="64"/>
@@ -8940,174 +8981,174 @@
     </row>
     <row r="33" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="43" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>162</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G33" s="45" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="H33" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>680</v>
+      </c>
+      <c r="J33" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="K33" s="43" t="s">
         <v>721</v>
-      </c>
-      <c r="I33" s="43" t="s">
-        <v>687</v>
-      </c>
-      <c r="J33" s="45" t="s">
-        <v>688</v>
-      </c>
-      <c r="K33" s="43" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>162</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="K37" s="3"/>
     </row>
     <row r="39" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="65" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="B39" s="64"/>
       <c r="C39" s="64"/>
@@ -9122,7 +9163,7 @@
     </row>
     <row r="40" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="87" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="B40" s="64"/>
       <c r="C40" s="64"/>
@@ -9137,7 +9178,7 @@
     </row>
     <row r="41" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="87" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B41" s="64"/>
       <c r="C41" s="64"/>
@@ -9152,7 +9193,7 @@
     </row>
     <row r="42" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="87" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="B42" s="64"/>
       <c r="C42" s="64"/>
@@ -9167,7 +9208,7 @@
     </row>
     <row r="43" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A43" s="87" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B43" s="64"/>
       <c r="C43" s="64"/>
@@ -9213,7 +9254,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -9231,7 +9272,7 @@
     </row>
     <row r="4" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -9241,7 +9282,7 @@
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="92" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="B8" s="64"/>
       <c r="C8" s="64"/>
@@ -9251,10 +9292,10 @@
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="59"/>
@@ -9263,10 +9304,10 @@
     </row>
     <row r="10" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C10" s="59"/>
       <c r="D10" s="59"/>
@@ -9275,7 +9316,7 @@
     </row>
     <row r="11" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B11" s="91" t="s">
         <v>220</v>
@@ -9287,10 +9328,10 @@
     </row>
     <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B12" s="80" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="C12" s="59"/>
       <c r="D12" s="59"/>
@@ -9299,19 +9340,19 @@
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E13" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F13" s="76"/>
     </row>
@@ -9327,48 +9368,48 @@
         <v>16</v>
       </c>
       <c r="E14" s="91" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F14" s="76"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="48"/>
       <c r="B15" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E15" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F15" s="76"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="48"/>
       <c r="B16" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E16" s="91" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="F16" s="76"/>
     </row>
     <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="C17" s="59"/>
       <c r="D17" s="59"/>
@@ -9377,7 +9418,7 @@
     </row>
     <row r="19" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="92" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="B19" s="64"/>
       <c r="C19" s="64"/>
@@ -9387,10 +9428,10 @@
     </row>
     <row r="20" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C20" s="59"/>
       <c r="D20" s="59"/>
@@ -9399,10 +9440,10 @@
     </row>
     <row r="21" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C21" s="59"/>
       <c r="D21" s="59"/>
@@ -9411,7 +9452,7 @@
     </row>
     <row r="22" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B22" s="91" t="s">
         <v>333</v>
@@ -9423,10 +9464,10 @@
     </row>
     <row r="23" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B23" s="80" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C23" s="59"/>
       <c r="D23" s="59"/>
@@ -9435,19 +9476,19 @@
     </row>
     <row r="24" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E24" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F24" s="76"/>
     </row>
@@ -9463,48 +9504,48 @@
         <v>16</v>
       </c>
       <c r="E25" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F25" s="76"/>
     </row>
     <row r="26" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="48"/>
       <c r="B26" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E26" s="91" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="F26" s="76"/>
     </row>
     <row r="27" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="48"/>
       <c r="B27" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E27" s="91" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="F27" s="76"/>
     </row>
     <row r="28" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B28" s="80" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C28" s="59"/>
       <c r="D28" s="59"/>
@@ -9513,7 +9554,7 @@
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="92" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="B30" s="64"/>
       <c r="C30" s="64"/>
@@ -9523,10 +9564,10 @@
     </row>
     <row r="31" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B31" s="80" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="C31" s="59"/>
       <c r="D31" s="59"/>
@@ -9535,10 +9576,10 @@
     </row>
     <row r="32" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B32" s="80" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="C32" s="59"/>
       <c r="D32" s="59"/>
@@ -9547,7 +9588,7 @@
     </row>
     <row r="33" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B33" s="91" t="s">
         <v>237</v>
@@ -9559,10 +9600,10 @@
     </row>
     <row r="34" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B34" s="80" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="C34" s="59"/>
       <c r="D34" s="59"/>
@@ -9571,19 +9612,19 @@
     </row>
     <row r="35" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E35" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F35" s="76"/>
     </row>
@@ -9599,48 +9640,48 @@
         <v>9</v>
       </c>
       <c r="E36" s="91" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F36" s="76"/>
     </row>
     <row r="37" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="48"/>
       <c r="B37" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E37" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F37" s="76"/>
     </row>
     <row r="38" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="48"/>
       <c r="B38" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="E38" s="91" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="F38" s="76"/>
     </row>
     <row r="39" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B39" s="80" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="C39" s="59"/>
       <c r="D39" s="59"/>
@@ -9649,7 +9690,7 @@
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="92" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B41" s="64"/>
       <c r="C41" s="64"/>
@@ -9659,10 +9700,10 @@
     </row>
     <row r="42" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B42" s="80" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="59"/>
@@ -9671,10 +9712,10 @@
     </row>
     <row r="43" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A43" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B43" s="80" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="C43" s="59"/>
       <c r="D43" s="59"/>
@@ -9683,7 +9724,7 @@
     </row>
     <row r="44" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A44" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B44" s="91" t="s">
         <v>230</v>
@@ -9695,10 +9736,10 @@
     </row>
     <row r="45" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B45" s="80" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="59"/>
@@ -9707,19 +9748,19 @@
     </row>
     <row r="46" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E46" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F46" s="76"/>
     </row>
@@ -9735,48 +9776,48 @@
         <v>16</v>
       </c>
       <c r="E47" s="91" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F47" s="76"/>
     </row>
     <row r="48" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="48"/>
       <c r="B48" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E48" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F48" s="76"/>
     </row>
     <row r="49" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="48"/>
       <c r="B49" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="E49" s="91" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="F49" s="76"/>
     </row>
     <row r="50" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B50" s="80" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="59"/>
@@ -9785,7 +9826,7 @@
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="92" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="B52" s="64"/>
       <c r="C52" s="64"/>
@@ -9795,10 +9836,10 @@
     </row>
     <row r="53" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B53" s="80" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="59"/>
@@ -9807,10 +9848,10 @@
     </row>
     <row r="54" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B54" s="80" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="C54" s="59"/>
       <c r="D54" s="59"/>
@@ -9819,7 +9860,7 @@
     </row>
     <row r="55" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B55" s="91" t="s">
         <v>241</v>
@@ -9831,10 +9872,10 @@
     </row>
     <row r="56" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B56" s="80" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="C56" s="59"/>
       <c r="D56" s="59"/>
@@ -9843,19 +9884,19 @@
     </row>
     <row r="57" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A57" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E57" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F57" s="76"/>
     </row>
@@ -9871,48 +9912,48 @@
         <v>16</v>
       </c>
       <c r="E58" s="91" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F58" s="76"/>
     </row>
     <row r="59" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="48"/>
       <c r="B59" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E59" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F59" s="76"/>
     </row>
     <row r="60" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="48"/>
       <c r="B60" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="E60" s="91" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="F60" s="76"/>
     </row>
     <row r="61" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B61" s="80" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="C61" s="59"/>
       <c r="D61" s="59"/>
@@ -9921,7 +9962,7 @@
     </row>
     <row r="63" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A63" s="92" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="B63" s="64"/>
       <c r="C63" s="64"/>
@@ -9931,10 +9972,10 @@
     </row>
     <row r="64" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="46" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B64" s="80" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -9943,10 +9984,10 @@
     </row>
     <row r="65" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="46" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B65" s="80" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="C65" s="59"/>
       <c r="D65" s="59"/>
@@ -9955,7 +9996,7 @@
     </row>
     <row r="66" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="46" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B66" s="91" t="s">
         <v>349</v>
@@ -9967,10 +10008,10 @@
     </row>
     <row r="67" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="46" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B67" s="80" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="C67" s="59"/>
       <c r="D67" s="59"/>
@@ -9979,19 +10020,19 @@
     </row>
     <row r="68" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="46" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E68" s="75" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F68" s="76"/>
     </row>
@@ -10007,48 +10048,48 @@
         <v>23</v>
       </c>
       <c r="E69" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F69" s="76"/>
     </row>
     <row r="70" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="48"/>
       <c r="B70" s="29" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E70" s="91" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="F70" s="76"/>
     </row>
     <row r="71" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="48"/>
       <c r="B71" s="29" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E71" s="91" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="F71" s="76"/>
     </row>
     <row r="72" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A72" s="46" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B72" s="80" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="C72" s="59"/>
       <c r="D72" s="59"/>
@@ -10138,7 +10179,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="63" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -10152,7 +10193,7 @@
     </row>
     <row r="4" spans="1:4" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -10160,7 +10201,7 @@
     </row>
     <row r="6" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="65" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
@@ -10168,217 +10209,217 @@
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="49" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="49" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="49" t="s">
+        <v>855</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>861</v>
+      </c>
+      <c r="C10" s="47" t="s">
         <v>862</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>868</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>869</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="33" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="33" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="33" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="33" t="s">
+        <v>864</v>
+      </c>
+      <c r="B14" s="47" t="s">
         <v>871</v>
       </c>
-      <c r="B14" s="47" t="s">
-        <v>878</v>
-      </c>
       <c r="C14" s="47" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="51" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="51" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="51" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="51" t="s">
+        <v>873</v>
+      </c>
+      <c r="B18" s="47" t="s">
         <v>880</v>
       </c>
-      <c r="B18" s="47" t="s">
-        <v>887</v>
-      </c>
       <c r="C18" s="47" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="52" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="52" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="52" t="s">
+        <v>882</v>
+      </c>
+      <c r="B21" s="50" t="s">
         <v>889</v>
       </c>
-      <c r="B21" s="50" t="s">
-        <v>896</v>
-      </c>
       <c r="C21" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="65" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="B24" s="64"/>
       <c r="C24" s="64"/>
@@ -10386,77 +10427,77 @@
     </row>
     <row r="25" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="29" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="53" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="29" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="53" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="65" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B31" s="64"/>
       <c r="C31" s="64"/>
@@ -10464,114 +10505,114 @@
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="29" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="53" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="29" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="53" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="C36" s="50" t="s">
         <v>162</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="29" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="53" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="29" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="B39" s="47" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -10617,7 +10658,7 @@
     </row>
     <row r="4" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="58" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -10655,7 +10696,7 @@
         <v>124</v>
       </c>
       <c r="B8" s="70" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>125</v>
@@ -10690,7 +10731,7 @@
         <v>131</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
@@ -10716,7 +10757,7 @@
         <v>126</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.5">
@@ -10802,7 +10843,7 @@
         <v>126</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -10815,7 +10856,7 @@
         <v>126</v>
       </c>
       <c r="E19" s="54" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -10867,7 +10908,7 @@
     </row>
     <row r="4" spans="1:6" ht="96" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="58" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -10999,7 +11040,7 @@
         <v>179</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>163</v>
@@ -11210,7 +11251,7 @@
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="58" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -11403,7 +11444,7 @@
     </row>
     <row r="4" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="58" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -11483,7 +11524,7 @@
         <v>224</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>225</v>
@@ -11613,7 +11654,7 @@
     </row>
     <row r="17" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="58" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="59"/>
@@ -11662,7 +11703,7 @@
     </row>
     <row r="4" spans="1:5" ht="84" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -12038,7 +12079,7 @@
     </row>
     <row r="4" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
@@ -12204,7 +12245,7 @@
     </row>
     <row r="4" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="68" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
